--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91820112</v>
+        <v>135488970</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751215</v>
+        <v>751297</v>
       </c>
       <c r="R2" t="n">
-        <v>7375871</v>
+        <v>7376037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91820093</v>
+        <v>135490783</v>
       </c>
       <c r="B3" t="n">
-        <v>92369</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751353</v>
+        <v>751373</v>
       </c>
       <c r="R3" t="n">
-        <v>7376123</v>
+        <v>7376101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91820113</v>
+        <v>135492457</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751208</v>
+        <v>751543</v>
       </c>
       <c r="R4" t="n">
-        <v>7375899</v>
+        <v>7376055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,15 +954,3371 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91820112</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79406</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>864</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751215</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7375871</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Sture Westerberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Håkan Falk</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>91820093</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>751353</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7376123</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91820113</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>751208</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7375899</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135494092</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101376</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>751697</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7375888</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135494212</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101376</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>751690</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7375884</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135494377</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101376</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>751681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7375876</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135494485</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101376</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>751677</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7375866</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135493935</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97308</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>751725</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7375905</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135494039</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97308</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>751706</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7375893</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135487454</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>751385</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7376134</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135487819</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>751340</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7376092</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135488053</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>751340</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7376082</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135488602</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>751370</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7376029</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135488683</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>751337</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7376020</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135493576</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>751658</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7376014</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135493529</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751644</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7376014</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135490400</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>751358</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7376019</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135487949</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack 1</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135492288</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>751533</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7376077</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135492904</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>751604</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7376073</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135488308</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7376070</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135493284</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>751617</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7376065</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135487574</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ett par i lämplig häckningsbiotop</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135491874</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751383</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135487999</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7376085</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135487698</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7376116</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135493447</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>751609</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7376039</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135487495</v>
+      </c>
+      <c r="B32" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>751361</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7376128</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135492620</v>
+      </c>
+      <c r="B33" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>751566</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135488283</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135492603</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>751552</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135487671</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7376126</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135488970</v>
+        <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>99193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751297</v>
+        <v>751279</v>
       </c>
       <c r="R2" t="n">
-        <v>7376037</v>
+        <v>7375962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135490783</v>
+        <v>135488970</v>
       </c>
       <c r="B3" t="n">
         <v>92245</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751373</v>
+        <v>751297</v>
       </c>
       <c r="R3" t="n">
-        <v>7376101</v>
+        <v>7376037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135492457</v>
+        <v>135490783</v>
       </c>
       <c r="B4" t="n">
         <v>92245</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751543</v>
+        <v>751373</v>
       </c>
       <c r="R4" t="n">
-        <v>7376055</v>
+        <v>7376101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91820112</v>
+        <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751215</v>
+        <v>751543</v>
       </c>
       <c r="R5" t="n">
-        <v>7375871</v>
+        <v>7376055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91820093</v>
+        <v>91820112</v>
       </c>
       <c r="B6" t="n">
-        <v>92369</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751353</v>
+        <v>751215</v>
       </c>
       <c r="R6" t="n">
-        <v>7376123</v>
+        <v>7375871</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91820113</v>
+        <v>91820093</v>
       </c>
       <c r="B7" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751208</v>
+        <v>751353</v>
       </c>
       <c r="R7" t="n">
-        <v>7375899</v>
+        <v>7376123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2020-08-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,45 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135494092</v>
+        <v>91820113</v>
       </c>
       <c r="B8" t="n">
-        <v>101376</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1365</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Övre Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751697</v>
+        <v>751208</v>
       </c>
       <c r="R8" t="n">
-        <v>7375888</v>
+        <v>7375899</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2020-08-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Håkan Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135494212</v>
+        <v>135511669</v>
       </c>
       <c r="B9" t="n">
-        <v>101376</v>
+        <v>79912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>751690</v>
+        <v>751320</v>
       </c>
       <c r="R9" t="n">
-        <v>7375884</v>
+        <v>7375962</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135494377</v>
+        <v>135494092</v>
       </c>
       <c r="B10" t="n">
         <v>101376</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751681</v>
+        <v>751697</v>
       </c>
       <c r="R10" t="n">
-        <v>7375876</v>
+        <v>7375888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135494485</v>
+        <v>135494212</v>
       </c>
       <c r="B11" t="n">
         <v>101376</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751677</v>
+        <v>751690</v>
       </c>
       <c r="R11" t="n">
-        <v>7375866</v>
+        <v>7375884</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135493935</v>
+        <v>135494377</v>
       </c>
       <c r="B12" t="n">
-        <v>97308</v>
+        <v>101376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751725</v>
+        <v>751681</v>
       </c>
       <c r="R12" t="n">
-        <v>7375905</v>
+        <v>7375876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135494039</v>
+        <v>135494485</v>
       </c>
       <c r="B13" t="n">
-        <v>97308</v>
+        <v>101376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751706</v>
+        <v>751677</v>
       </c>
       <c r="R13" t="n">
-        <v>7375893</v>
+        <v>7375866</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135487454</v>
+        <v>135512295</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>101376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751385</v>
+        <v>751362</v>
       </c>
       <c r="R14" t="n">
-        <v>7376134</v>
+        <v>7375922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135487819</v>
+        <v>135513277</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>101376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751340</v>
+        <v>751608</v>
       </c>
       <c r="R15" t="n">
-        <v>7376092</v>
+        <v>7375832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135488053</v>
+        <v>135513622</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>101376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751340</v>
+        <v>751666</v>
       </c>
       <c r="R16" t="n">
-        <v>7376082</v>
+        <v>7375784</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135488602</v>
+        <v>135512444</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>96678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751370</v>
+        <v>751407</v>
       </c>
       <c r="R17" t="n">
-        <v>7376029</v>
+        <v>7375917</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135488683</v>
+        <v>135493935</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>97308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751337</v>
+        <v>751725</v>
       </c>
       <c r="R18" t="n">
-        <v>7376020</v>
+        <v>7375905</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135493576</v>
+        <v>135494039</v>
       </c>
       <c r="B19" t="n">
-        <v>79397</v>
+        <v>97308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751658</v>
+        <v>751706</v>
       </c>
       <c r="R19" t="n">
-        <v>7376014</v>
+        <v>7375893</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135493529</v>
+        <v>135487454</v>
       </c>
       <c r="B20" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751644</v>
+        <v>751385</v>
       </c>
       <c r="R20" t="n">
-        <v>7376014</v>
+        <v>7376134</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135490400</v>
+        <v>135487819</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751358</v>
+        <v>751340</v>
       </c>
       <c r="R21" t="n">
-        <v>7376019</v>
+        <v>7376092</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2589,11 +2589,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2620,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135487949</v>
+        <v>135488053</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751338</v>
+        <v>751340</v>
       </c>
       <c r="R22" t="n">
-        <v>7376087</v>
+        <v>7376082</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2691,11 +2686,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2722,50 +2712,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135492288</v>
+        <v>135488602</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751533</v>
+        <v>751370</v>
       </c>
       <c r="R23" t="n">
-        <v>7376077</v>
+        <v>7376029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2798,11 +2783,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2829,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135492904</v>
+        <v>135488683</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751604</v>
+        <v>751337</v>
       </c>
       <c r="R24" t="n">
-        <v>7376073</v>
+        <v>7376020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2900,11 +2880,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,57 +2906,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135488308</v>
+        <v>135510447</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751354</v>
+        <v>751269</v>
       </c>
       <c r="R25" t="n">
-        <v>7376070</v>
+        <v>7375976</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3005,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3037,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135493284</v>
+        <v>135493576</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>79397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3072,13 +3038,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751617</v>
+        <v>751658</v>
       </c>
       <c r="R26" t="n">
-        <v>7376065</v>
+        <v>7376014</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3134,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135487574</v>
+        <v>135493529</v>
       </c>
       <c r="B27" t="n">
-        <v>58678</v>
+        <v>80492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3145,41 +3111,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103056</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751357</v>
+        <v>751644</v>
       </c>
       <c r="R27" t="n">
-        <v>7376129</v>
+        <v>7376014</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3209,11 +3171,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ett par i lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3240,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135491874</v>
+        <v>135513861</v>
       </c>
       <c r="B28" t="n">
-        <v>5201</v>
+        <v>80492</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3275,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751383</v>
+        <v>751610</v>
       </c>
       <c r="R28" t="n">
-        <v>7376129</v>
+        <v>7375777</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3305,17 +3262,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3342,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135487999</v>
+        <v>135511907</v>
       </c>
       <c r="B29" t="n">
-        <v>8449</v>
+        <v>80500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3353,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3380,7 +3332,7 @@
         <v>751338</v>
       </c>
       <c r="R29" t="n">
-        <v>7376085</v>
+        <v>7375957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,17 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3444,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135487698</v>
+        <v>135490400</v>
       </c>
       <c r="B30" t="n">
-        <v>98219</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3455,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219815</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3479,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751357</v>
+        <v>751358</v>
       </c>
       <c r="R30" t="n">
-        <v>7376116</v>
+        <v>7376019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3515,6 +3462,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3541,32 +3493,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135493447</v>
+        <v>135487949</v>
       </c>
       <c r="B31" t="n">
-        <v>108205</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220083</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3576,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751609</v>
+        <v>751338</v>
       </c>
       <c r="R31" t="n">
-        <v>7376039</v>
+        <v>7376087</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3612,6 +3564,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3638,45 +3595,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135487495</v>
+        <v>135492288</v>
       </c>
       <c r="B32" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751361</v>
+        <v>751533</v>
       </c>
       <c r="R32" t="n">
-        <v>7376128</v>
+        <v>7376077</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3709,6 +3671,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3735,32 +3702,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135492620</v>
+        <v>135492904</v>
       </c>
       <c r="B33" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3770,10 +3737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751566</v>
+        <v>751604</v>
       </c>
       <c r="R33" t="n">
-        <v>7376059</v>
+        <v>7376073</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3806,6 +3773,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3832,45 +3804,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135488283</v>
+        <v>135508817</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751338</v>
+        <v>751185</v>
       </c>
       <c r="R34" t="n">
-        <v>7376087</v>
+        <v>7375925</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,17 +3874,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3934,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135492603</v>
+        <v>135508144</v>
       </c>
       <c r="B35" t="n">
-        <v>99195</v>
+        <v>5181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3969,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751552</v>
+        <v>751233</v>
       </c>
       <c r="R35" t="n">
-        <v>7376059</v>
+        <v>7375939</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3999,12 +3976,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135487671</v>
+        <v>135511007</v>
       </c>
       <c r="B36" t="n">
-        <v>98060</v>
+        <v>12373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>101283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4066,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751354</v>
+        <v>751283</v>
       </c>
       <c r="R36" t="n">
-        <v>7376126</v>
+        <v>7375962</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4096,12 +4078,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4128,45 +4115,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135488071</v>
+        <v>135508608</v>
       </c>
       <c r="B37" t="n">
-        <v>99217</v>
+        <v>12573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>101691</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751342</v>
+        <v>751209</v>
       </c>
       <c r="R37" t="n">
-        <v>7376081</v>
+        <v>7375929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4193,12 +4189,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4225,32 +4221,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135491240</v>
+        <v>135514248</v>
       </c>
       <c r="B38" t="n">
-        <v>98249</v>
+        <v>12573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>223358</v>
+        <v>101691</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4260,10 +4256,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751305</v>
+        <v>751562</v>
       </c>
       <c r="R38" t="n">
-        <v>7376101</v>
+        <v>7375703</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,12 +4286,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4319,6 +4315,1887 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135488308</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7376070</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135493284</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>751617</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7376065</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135487574</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ett par i lämplig häckningsbiotop</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135491874</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>751383</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135508160</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>751232</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7375940</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135487999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7376085</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135487698</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7376116</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135493447</v>
+      </c>
+      <c r="B46" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>751609</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7376039</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135511789</v>
+      </c>
+      <c r="B47" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>751333</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7375966</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135487495</v>
+      </c>
+      <c r="B48" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>751361</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7376128</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135492620</v>
+      </c>
+      <c r="B49" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>751566</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135512174</v>
+      </c>
+      <c r="B50" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>751350</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7375940</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135488283</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135492603</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>751552</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135510422</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>751264</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7375973</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135487671</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7376126</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511421</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135490783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492457</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820112</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820093</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494092</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494212</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494485</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512295</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513277</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513622</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512444</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493935</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494039</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487454</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487819</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488053</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488602</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488683</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,35 +3120,40 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510447</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135493576</v>
+        <v>135567074</v>
       </c>
       <c r="B26" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751658</v>
+        <v>751757</v>
       </c>
       <c r="R26" t="n">
-        <v>7376014</v>
+        <v>7375888</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3193,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3097,13 +3222,18 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135567074</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135493529</v>
+        <v>135493576</v>
       </c>
       <c r="B27" t="n">
-        <v>80492</v>
+        <v>79397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,7 +3265,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751644</v>
+        <v>751658</v>
       </c>
       <c r="R27" t="n">
         <v>7376014</v>
@@ -3194,10 +3324,15 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493576</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135513861</v>
+        <v>135493529</v>
       </c>
       <c r="B28" t="n">
         <v>80492</v>
@@ -3232,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751610</v>
+        <v>751644</v>
       </c>
       <c r="R28" t="n">
-        <v>7375777</v>
+        <v>7376014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3262,12 +3397,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3291,13 +3426,18 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493529</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135511907</v>
+        <v>135513861</v>
       </c>
       <c r="B29" t="n">
-        <v>80500</v>
+        <v>80492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>751338</v>
+        <v>751610</v>
       </c>
       <c r="R29" t="n">
-        <v>7375957</v>
+        <v>7375777</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3388,13 +3528,18 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513861</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135490400</v>
+        <v>135511907</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>80500</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3402,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751358</v>
+        <v>751338</v>
       </c>
       <c r="R30" t="n">
-        <v>7376019</v>
+        <v>7375957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3456,17 +3601,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3490,30 +3630,35 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511907</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135487949</v>
+        <v>135490400</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3528,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751338</v>
+        <v>751358</v>
       </c>
       <c r="R31" t="n">
-        <v>7376087</v>
+        <v>7376019</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,7 +3713,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack 1</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,10 +3737,15 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135490400</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135492288</v>
+        <v>135487949</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3624,21 +3774,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751533</v>
+        <v>751338</v>
       </c>
       <c r="R32" t="n">
-        <v>7376077</v>
+        <v>7376087</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3675,7 +3820,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3699,10 +3844,15 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487949</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135492904</v>
+        <v>135492288</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3731,16 +3881,21 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751604</v>
+        <v>751533</v>
       </c>
       <c r="R33" t="n">
-        <v>7376073</v>
+        <v>7376077</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3777,7 +3932,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3801,10 +3956,15 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492288</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135508817</v>
+        <v>135492904</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3833,21 +3993,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751185</v>
+        <v>751604</v>
       </c>
       <c r="R34" t="n">
-        <v>7375925</v>
+        <v>7376073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3874,17 +4029,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3908,48 +4063,58 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492904</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135508144</v>
+        <v>135508817</v>
       </c>
       <c r="B35" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751233</v>
+        <v>751185</v>
       </c>
       <c r="R35" t="n">
-        <v>7375939</v>
+        <v>7375925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3986,7 +4151,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4010,35 +4175,40 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508817</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135511007</v>
+        <v>135508144</v>
       </c>
       <c r="B36" t="n">
-        <v>12373</v>
+        <v>5181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101283</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4218,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751283</v>
+        <v>751233</v>
       </c>
       <c r="R36" t="n">
-        <v>7375962</v>
+        <v>7375939</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4088,7 +4258,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4112,57 +4282,53 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508144</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135508608</v>
+        <v>135511007</v>
       </c>
       <c r="B37" t="n">
-        <v>12573</v>
+        <v>12373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101691</v>
+        <v>101283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751209</v>
+        <v>751283</v>
       </c>
       <c r="R37" t="n">
-        <v>7375929</v>
+        <v>7375962</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4197,6 +4363,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4218,35 +4389,40 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511007</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135514248</v>
+        <v>135566886</v>
       </c>
       <c r="B38" t="n">
-        <v>12573</v>
+        <v>12373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101691</v>
+        <v>101283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4256,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751562</v>
+        <v>751705</v>
       </c>
       <c r="R38" t="n">
-        <v>7375703</v>
+        <v>7375824</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4286,12 +4462,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4315,35 +4496,40 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135566886</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135488308</v>
+        <v>135508608</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>12573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4353,7 +4539,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4362,13 +4548,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751354</v>
+        <v>751209</v>
       </c>
       <c r="R39" t="n">
-        <v>7376070</v>
+        <v>7375929</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4392,12 +4578,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4421,35 +4607,40 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508608</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135493284</v>
+        <v>135514248</v>
       </c>
       <c r="B40" t="n">
-        <v>58136</v>
+        <v>12573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4459,13 +4650,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751617</v>
+        <v>751562</v>
       </c>
       <c r="R40" t="n">
-        <v>7376065</v>
+        <v>7375703</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4489,12 +4680,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4518,55 +4709,56 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135514248</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135487574</v>
+        <v>135571094</v>
       </c>
       <c r="B41" t="n">
-        <v>58678</v>
+        <v>5180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103056</v>
+        <v>102204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751357</v>
+        <v>751322</v>
       </c>
       <c r="R41" t="n">
-        <v>7376129</v>
+        <v>7375956</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4590,17 +4782,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ett par i lämplig häckningsbiotop</t>
+          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4624,51 +4816,65 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135571094</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135491874</v>
+        <v>135488308</v>
       </c>
       <c r="B42" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751383</v>
+        <v>751354</v>
       </c>
       <c r="R42" t="n">
-        <v>7376129</v>
+        <v>7376070</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4698,11 +4904,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4726,35 +4927,40 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488308</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135508160</v>
+        <v>135493284</v>
       </c>
       <c r="B43" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4764,13 +4970,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751232</v>
+        <v>751617</v>
       </c>
       <c r="R43" t="n">
-        <v>7375940</v>
+        <v>7376065</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4794,17 +5000,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4828,13 +5029,18 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493284</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135487999</v>
+        <v>135487574</v>
       </c>
       <c r="B44" t="n">
-        <v>8449</v>
+        <v>58678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,37 +5048,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>103056</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751338</v>
+        <v>751357</v>
       </c>
       <c r="R44" t="n">
-        <v>7376085</v>
+        <v>7376129</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4906,7 +5116,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Ett par i lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4930,13 +5140,18 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487574</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135487698</v>
+        <v>135491874</v>
       </c>
       <c r="B45" t="n">
-        <v>98219</v>
+        <v>5201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4944,21 +5159,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219815</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4968,10 +5183,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751357</v>
+        <v>751383</v>
       </c>
       <c r="R45" t="n">
-        <v>7376116</v>
+        <v>7376129</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5006,6 +5221,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5027,13 +5247,18 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491874</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135493447</v>
+        <v>135508160</v>
       </c>
       <c r="B46" t="n">
-        <v>108205</v>
+        <v>5201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5041,21 +5266,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220083</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5065,10 +5290,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751609</v>
+        <v>751232</v>
       </c>
       <c r="R46" t="n">
-        <v>7376039</v>
+        <v>7375940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5095,12 +5320,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5124,13 +5354,18 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508160</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135511789</v>
+        <v>135487999</v>
       </c>
       <c r="B47" t="n">
-        <v>108205</v>
+        <v>8449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5138,21 +5373,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220083</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5162,10 +5397,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751333</v>
+        <v>751338</v>
       </c>
       <c r="R47" t="n">
-        <v>7375966</v>
+        <v>7376085</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5192,12 +5427,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5221,13 +5461,18 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487999</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135487495</v>
+        <v>135487698</v>
       </c>
       <c r="B48" t="n">
-        <v>111153</v>
+        <v>98219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5235,21 +5480,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220240</v>
+        <v>219815</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5259,10 +5504,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751361</v>
+        <v>751357</v>
       </c>
       <c r="R48" t="n">
-        <v>7376128</v>
+        <v>7376116</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,13 +5563,18 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487698</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135492620</v>
+        <v>135493447</v>
       </c>
       <c r="B49" t="n">
-        <v>111153</v>
+        <v>108205</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5332,21 +5582,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5356,10 +5606,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751566</v>
+        <v>751609</v>
       </c>
       <c r="R49" t="n">
-        <v>7376059</v>
+        <v>7376039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5415,13 +5665,18 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493447</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135512174</v>
+        <v>135511789</v>
       </c>
       <c r="B50" t="n">
-        <v>111153</v>
+        <v>108205</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5429,21 +5684,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5453,10 +5708,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751350</v>
+        <v>751333</v>
       </c>
       <c r="R50" t="n">
-        <v>7375940</v>
+        <v>7375966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5512,35 +5767,40 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135488283</v>
+        <v>135487495</v>
       </c>
       <c r="B51" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5550,10 +5810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751338</v>
+        <v>751361</v>
       </c>
       <c r="R51" t="n">
-        <v>7376087</v>
+        <v>7376128</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5588,11 +5848,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5614,35 +5869,40 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487495</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135492603</v>
+        <v>135492620</v>
       </c>
       <c r="B52" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5652,7 +5912,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751552</v>
+        <v>751566</v>
       </c>
       <c r="R52" t="n">
         <v>7376059</v>
@@ -5711,13 +5971,18 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492620</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135510422</v>
+        <v>135512174</v>
       </c>
       <c r="B53" t="n">
-        <v>106309</v>
+        <v>111153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5725,21 +5990,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221725</v>
+        <v>220240</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5749,10 +6014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751264</v>
+        <v>751350</v>
       </c>
       <c r="R53" t="n">
-        <v>7375973</v>
+        <v>7375940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5808,35 +6073,40 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512174</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135487671</v>
+        <v>135488283</v>
       </c>
       <c r="B54" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5846,10 +6116,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751354</v>
+        <v>751338</v>
       </c>
       <c r="R54" t="n">
-        <v>7376126</v>
+        <v>7376087</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5884,6 +6154,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5905,35 +6180,40 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488283</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135488071</v>
+        <v>135492603</v>
       </c>
       <c r="B55" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5943,10 +6223,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751342</v>
+        <v>751552</v>
       </c>
       <c r="R55" t="n">
-        <v>7376081</v>
+        <v>7376059</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,13 +6282,18 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492603</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135511436</v>
+        <v>135510422</v>
       </c>
       <c r="B56" t="n">
-        <v>99001</v>
+        <v>106309</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6016,21 +6301,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223049</v>
+        <v>221725</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6040,10 +6325,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751315</v>
+        <v>751264</v>
       </c>
       <c r="R56" t="n">
-        <v>7375971</v>
+        <v>7375973</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6099,13 +6384,18 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510422</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135491240</v>
+        <v>135487671</v>
       </c>
       <c r="B57" t="n">
-        <v>98249</v>
+        <v>98060</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6113,21 +6403,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223358</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6137,10 +6427,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751305</v>
+        <v>751354</v>
       </c>
       <c r="R57" t="n">
-        <v>7376101</v>
+        <v>7376126</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6196,8 +6486,380 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487671</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488071</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511436</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2210,48 +2210,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135512444</v>
+        <v>135602165</v>
       </c>
       <c r="B17" t="n">
-        <v>96678</v>
+        <v>92167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2166</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751407</v>
+        <v>751313</v>
       </c>
       <c r="R17" t="n">
-        <v>7375917</v>
+        <v>7376133</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,16 +2306,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512444</t>
+          <t>https://artportalen.se/Sighting/135602165</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135493935</v>
+        <v>135512444</v>
       </c>
       <c r="B18" t="n">
-        <v>97308</v>
+        <v>96678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>2166</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751725</v>
+        <v>751407</v>
       </c>
       <c r="R18" t="n">
-        <v>7375905</v>
+        <v>7375917</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2408,13 +2408,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493935</t>
+          <t>https://artportalen.se/Sighting/135512444</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135494039</v>
+        <v>135493935</v>
       </c>
       <c r="B19" t="n">
         <v>97308</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751706</v>
+        <v>751725</v>
       </c>
       <c r="R19" t="n">
-        <v>7375893</v>
+        <v>7375905</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,38 +2510,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494039</t>
+          <t>https://artportalen.se/Sighting/135493935</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135487454</v>
+        <v>135494039</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>97308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751385</v>
+        <v>751706</v>
       </c>
       <c r="R20" t="n">
-        <v>7376134</v>
+        <v>7375893</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,54 +2612,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487454</t>
+          <t>https://artportalen.se/Sighting/135494039</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135487819</v>
+        <v>135602205</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>97308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751340</v>
+        <v>751335</v>
       </c>
       <c r="R21" t="n">
-        <v>7376092</v>
+        <v>7376158</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,13 +2714,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487819</t>
+          <t>https://artportalen.se/Sighting/135602205</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135488053</v>
+        <v>135487454</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751340</v>
+        <v>751385</v>
       </c>
       <c r="R22" t="n">
-        <v>7376082</v>
+        <v>7376134</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,13 +2816,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488053</t>
+          <t>https://artportalen.se/Sighting/135487454</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135488602</v>
+        <v>135487819</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751370</v>
+        <v>751340</v>
       </c>
       <c r="R23" t="n">
-        <v>7376029</v>
+        <v>7376092</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,13 +2918,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488602</t>
+          <t>https://artportalen.se/Sighting/135487819</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135488683</v>
+        <v>135488053</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751337</v>
+        <v>751340</v>
       </c>
       <c r="R24" t="n">
-        <v>7376020</v>
+        <v>7376082</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,13 +3020,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488683</t>
+          <t>https://artportalen.se/Sighting/135488053</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135510447</v>
+        <v>135488602</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751269</v>
+        <v>751370</v>
       </c>
       <c r="R25" t="n">
-        <v>7375976</v>
+        <v>7376029</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3091,12 +3091,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,13 +3122,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510447</t>
+          <t>https://artportalen.se/Sighting/135488602</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135567074</v>
+        <v>135488683</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751757</v>
+        <v>751337</v>
       </c>
       <c r="R26" t="n">
-        <v>7375888</v>
+        <v>7376020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3224,38 +3224,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135567074</t>
+          <t>https://artportalen.se/Sighting/135488683</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135493576</v>
+        <v>135510447</v>
       </c>
       <c r="B27" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751658</v>
+        <v>751269</v>
       </c>
       <c r="R27" t="n">
-        <v>7376014</v>
+        <v>7375976</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3326,38 +3326,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493576</t>
+          <t>https://artportalen.se/Sighting/135510447</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135493529</v>
+        <v>135567074</v>
       </c>
       <c r="B28" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751644</v>
+        <v>751757</v>
       </c>
       <c r="R28" t="n">
-        <v>7376014</v>
+        <v>7375888</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,54 +3428,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493529</t>
+          <t>https://artportalen.se/Sighting/135567074</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135513861</v>
+        <v>135602198</v>
       </c>
       <c r="B29" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>751610</v>
+        <v>751306</v>
       </c>
       <c r="R29" t="n">
-        <v>7375777</v>
+        <v>7376118</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3530,16 +3530,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513861</t>
+          <t>https://artportalen.se/Sighting/135602198</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135511907</v>
+        <v>135493576</v>
       </c>
       <c r="B30" t="n">
-        <v>80500</v>
+        <v>79397</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751338</v>
+        <v>751658</v>
       </c>
       <c r="R30" t="n">
-        <v>7375957</v>
+        <v>7376014</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3632,16 +3632,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511907</t>
+          <t>https://artportalen.se/Sighting/135493576</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135490400</v>
+        <v>135493529</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>80492</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751358</v>
+        <v>751644</v>
       </c>
       <c r="R31" t="n">
-        <v>7376019</v>
+        <v>7376014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3711,11 +3711,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3739,38 +3734,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135490400</t>
+          <t>https://artportalen.se/Sighting/135493529</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135487949</v>
+        <v>135513861</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751338</v>
+        <v>751610</v>
       </c>
       <c r="R32" t="n">
-        <v>7376087</v>
+        <v>7375777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3810,17 +3805,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3846,56 +3836,51 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487949</t>
+          <t>https://artportalen.se/Sighting/135513861</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135492288</v>
+        <v>135511907</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751533</v>
+        <v>751338</v>
       </c>
       <c r="R33" t="n">
-        <v>7376077</v>
+        <v>7375957</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3922,17 +3907,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3958,33 +3938,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492288</t>
+          <t>https://artportalen.se/Sighting/135511907</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135492904</v>
+        <v>135490400</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3999,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751604</v>
+        <v>751358</v>
       </c>
       <c r="R34" t="n">
-        <v>7376073</v>
+        <v>7376019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4039,7 +4019,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4065,13 +4045,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492904</t>
+          <t>https://artportalen.se/Sighting/135490400</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135508817</v>
+        <v>135487949</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4100,21 +4080,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751185</v>
+        <v>751338</v>
       </c>
       <c r="R35" t="n">
-        <v>7375925</v>
+        <v>7376087</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4141,17 +4116,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4177,51 +4152,56 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508817</t>
+          <t>https://artportalen.se/Sighting/135487949</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135508144</v>
+        <v>135492288</v>
       </c>
       <c r="B36" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751233</v>
+        <v>751533</v>
       </c>
       <c r="R36" t="n">
-        <v>7375939</v>
+        <v>7376077</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,17 +4228,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4284,38 +4264,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508144</t>
+          <t>https://artportalen.se/Sighting/135492288</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135511007</v>
+        <v>135492904</v>
       </c>
       <c r="B37" t="n">
-        <v>12373</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4325,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751283</v>
+        <v>751604</v>
       </c>
       <c r="R37" t="n">
-        <v>7375962</v>
+        <v>7376073</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,17 +4335,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4391,51 +4371,56 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511007</t>
+          <t>https://artportalen.se/Sighting/135492904</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135566886</v>
+        <v>135508817</v>
       </c>
       <c r="B38" t="n">
-        <v>12373</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751705</v>
+        <v>751185</v>
       </c>
       <c r="R38" t="n">
-        <v>7375824</v>
+        <v>7375925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4462,17 +4447,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4498,60 +4483,51 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135566886</t>
+          <t>https://artportalen.se/Sighting/135508817</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135508608</v>
+        <v>135508144</v>
       </c>
       <c r="B39" t="n">
-        <v>12573</v>
+        <v>5181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>101691</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751209</v>
+        <v>751233</v>
       </c>
       <c r="R39" t="n">
-        <v>7375929</v>
+        <v>7375939</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4586,6 +4562,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4609,38 +4590,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508608</t>
+          <t>https://artportalen.se/Sighting/135508144</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135514248</v>
+        <v>135511007</v>
       </c>
       <c r="B40" t="n">
-        <v>12573</v>
+        <v>12373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101691</v>
+        <v>101283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4650,10 +4631,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751562</v>
+        <v>751283</v>
       </c>
       <c r="R40" t="n">
-        <v>7375703</v>
+        <v>7375962</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4688,6 +4669,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4711,54 +4697,54 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135514248</t>
+          <t>https://artportalen.se/Sighting/135511007</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135571094</v>
+        <v>135566886</v>
       </c>
       <c r="B41" t="n">
-        <v>5180</v>
+        <v>12373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102204</v>
+        <v>101283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751322</v>
+        <v>751705</v>
       </c>
       <c r="R41" t="n">
-        <v>7375956</v>
+        <v>7375824</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4782,17 +4768,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
+          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4818,38 +4804,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135571094</t>
+          <t>https://artportalen.se/Sighting/135566886</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135488308</v>
+        <v>135508608</v>
       </c>
       <c r="B42" t="n">
-        <v>58136</v>
+        <v>12573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4859,7 +4845,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4868,13 +4854,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751354</v>
+        <v>751209</v>
       </c>
       <c r="R42" t="n">
-        <v>7376070</v>
+        <v>7375929</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4898,12 +4884,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4929,38 +4915,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488308</t>
+          <t>https://artportalen.se/Sighting/135508608</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135493284</v>
+        <v>135514248</v>
       </c>
       <c r="B43" t="n">
-        <v>58136</v>
+        <v>12573</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4970,13 +4956,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751617</v>
+        <v>751562</v>
       </c>
       <c r="R43" t="n">
-        <v>7376065</v>
+        <v>7375703</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5000,12 +4986,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5031,58 +5017,54 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493284</t>
+          <t>https://artportalen.se/Sighting/135514248</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135487574</v>
+        <v>135571094</v>
       </c>
       <c r="B44" t="n">
-        <v>58678</v>
+        <v>5180</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103056</v>
+        <v>102204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751357</v>
+        <v>751322</v>
       </c>
       <c r="R44" t="n">
-        <v>7376129</v>
+        <v>7375956</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5106,17 +5088,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ett par i lämplig häckningsbiotop</t>
+          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5142,54 +5124,63 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487574</t>
+          <t>https://artportalen.se/Sighting/135571094</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135491874</v>
+        <v>135488308</v>
       </c>
       <c r="B45" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751383</v>
+        <v>751354</v>
       </c>
       <c r="R45" t="n">
-        <v>7376129</v>
+        <v>7376070</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5219,11 +5210,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5249,38 +5235,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491874</t>
+          <t>https://artportalen.se/Sighting/135488308</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135508160</v>
+        <v>135493284</v>
       </c>
       <c r="B46" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5290,13 +5276,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751232</v>
+        <v>751617</v>
       </c>
       <c r="R46" t="n">
-        <v>7375940</v>
+        <v>7376065</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5320,17 +5306,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5356,16 +5337,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508160</t>
+          <t>https://artportalen.se/Sighting/135493284</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135487999</v>
+        <v>135487574</v>
       </c>
       <c r="B47" t="n">
-        <v>8449</v>
+        <v>58678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5373,37 +5354,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>103056</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751338</v>
+        <v>751357</v>
       </c>
       <c r="R47" t="n">
-        <v>7376085</v>
+        <v>7376129</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5437,7 +5422,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Ett par i lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5463,16 +5448,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487999</t>
+          <t>https://artportalen.se/Sighting/135487574</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135487698</v>
+        <v>135491874</v>
       </c>
       <c r="B48" t="n">
-        <v>98219</v>
+        <v>5201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5480,21 +5465,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219815</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5504,10 +5489,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751357</v>
+        <v>751383</v>
       </c>
       <c r="R48" t="n">
-        <v>7376116</v>
+        <v>7376129</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5542,6 +5527,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5565,16 +5555,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135491874</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135493447</v>
+        <v>135508160</v>
       </c>
       <c r="B49" t="n">
-        <v>108205</v>
+        <v>5201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5582,21 +5572,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220083</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5606,10 +5596,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751609</v>
+        <v>751232</v>
       </c>
       <c r="R49" t="n">
-        <v>7376039</v>
+        <v>7375940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,12 +5626,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5667,16 +5662,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135508160</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135511789</v>
+        <v>135487999</v>
       </c>
       <c r="B50" t="n">
-        <v>108205</v>
+        <v>8449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5684,21 +5679,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220083</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5708,10 +5703,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751333</v>
+        <v>751338</v>
       </c>
       <c r="R50" t="n">
-        <v>7375966</v>
+        <v>7376085</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5738,12 +5733,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5769,16 +5769,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135487999</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135487495</v>
+        <v>135487698</v>
       </c>
       <c r="B51" t="n">
-        <v>111153</v>
+        <v>98219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5786,21 +5786,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220240</v>
+        <v>219815</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751361</v>
+        <v>751357</v>
       </c>
       <c r="R51" t="n">
-        <v>7376128</v>
+        <v>7376116</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5871,16 +5871,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135492620</v>
+        <v>135493447</v>
       </c>
       <c r="B52" t="n">
-        <v>111153</v>
+        <v>108205</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5888,21 +5888,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751566</v>
+        <v>751609</v>
       </c>
       <c r="R52" t="n">
-        <v>7376059</v>
+        <v>7376039</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5973,16 +5973,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135512174</v>
+        <v>135511789</v>
       </c>
       <c r="B53" t="n">
-        <v>111153</v>
+        <v>108205</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751350</v>
+        <v>751333</v>
       </c>
       <c r="R53" t="n">
-        <v>7375940</v>
+        <v>7375966</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6075,38 +6075,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135488283</v>
+        <v>135487495</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751338</v>
+        <v>751361</v>
       </c>
       <c r="R54" t="n">
-        <v>7376087</v>
+        <v>7376128</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6154,11 +6154,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6182,38 +6177,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135492603</v>
+        <v>135492620</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6223,7 +6218,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751552</v>
+        <v>751566</v>
       </c>
       <c r="R55" t="n">
         <v>7376059</v>
@@ -6284,16 +6279,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135510422</v>
+        <v>135512174</v>
       </c>
       <c r="B56" t="n">
-        <v>106309</v>
+        <v>111153</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6301,21 +6296,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221725</v>
+        <v>220240</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6325,10 +6320,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751264</v>
+        <v>751350</v>
       </c>
       <c r="R56" t="n">
-        <v>7375973</v>
+        <v>7375940</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6386,38 +6381,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135487671</v>
+        <v>135488283</v>
       </c>
       <c r="B57" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6427,10 +6422,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751354</v>
+        <v>751338</v>
       </c>
       <c r="R57" t="n">
-        <v>7376126</v>
+        <v>7376087</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6465,6 +6460,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6488,38 +6488,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135488071</v>
+        <v>135492603</v>
       </c>
       <c r="B58" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>751342</v>
+        <v>751552</v>
       </c>
       <c r="R58" t="n">
-        <v>7376081</v>
+        <v>7376059</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6590,16 +6590,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135511436</v>
+        <v>135510422</v>
       </c>
       <c r="B59" t="n">
-        <v>99001</v>
+        <v>106309</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6607,21 +6607,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223049</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>751315</v>
+        <v>751264</v>
       </c>
       <c r="R59" t="n">
-        <v>7375971</v>
+        <v>7375973</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6692,16 +6692,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135491240</v>
+        <v>135487671</v>
       </c>
       <c r="B60" t="n">
-        <v>98249</v>
+        <v>98060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>223358</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751305</v>
+        <v>751354</v>
       </c>
       <c r="R60" t="n">
-        <v>7376101</v>
+        <v>7376126</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,7 +6794,420 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135487671</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488071</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511436</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135602173</t>
         </is>
       </c>
     </row>
@@ -6859,6 +7272,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ64"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>99193</v>
+        <v>99240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135511669</v>
       </c>
       <c r="B9" t="n">
-        <v>79912</v>
+        <v>79950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,32 +1496,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135494092</v>
+        <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>101376</v>
+        <v>79950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751697</v>
+        <v>751275</v>
       </c>
       <c r="R10" t="n">
-        <v>7375888</v>
+        <v>7376009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1561,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,38 +1597,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494092</t>
+          <t>https://artportalen.se/Sighting/135668795</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135494212</v>
+        <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>101376</v>
+        <v>79950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751690</v>
+        <v>751426</v>
       </c>
       <c r="R11" t="n">
-        <v>7375884</v>
+        <v>7376039</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,12 +1668,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,16 +1704,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494212</t>
+          <t>https://artportalen.se/Sighting/135671559</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135494377</v>
+        <v>135494092</v>
       </c>
       <c r="B12" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751681</v>
+        <v>751697</v>
       </c>
       <c r="R12" t="n">
-        <v>7375876</v>
+        <v>7375888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,16 +1806,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494377</t>
+          <t>https://artportalen.se/Sighting/135494092</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135494485</v>
+        <v>135494212</v>
       </c>
       <c r="B13" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751677</v>
+        <v>751690</v>
       </c>
       <c r="R13" t="n">
-        <v>7375866</v>
+        <v>7375884</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,16 +1908,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494485</t>
+          <t>https://artportalen.se/Sighting/135494212</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135512295</v>
+        <v>135494377</v>
       </c>
       <c r="B14" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751362</v>
+        <v>751681</v>
       </c>
       <c r="R14" t="n">
-        <v>7375922</v>
+        <v>7375876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1979,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,16 +2010,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512295</t>
+          <t>https://artportalen.se/Sighting/135494377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135513277</v>
+        <v>135494485</v>
       </c>
       <c r="B15" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751608</v>
+        <v>751677</v>
       </c>
       <c r="R15" t="n">
-        <v>7375832</v>
+        <v>7375866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2081,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,16 +2112,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513277</t>
+          <t>https://artportalen.se/Sighting/135494485</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135513622</v>
+        <v>135512295</v>
       </c>
       <c r="B16" t="n">
-        <v>101376</v>
+        <v>101424</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751666</v>
+        <v>751362</v>
       </c>
       <c r="R16" t="n">
-        <v>7375784</v>
+        <v>7375922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,54 +2214,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513622</t>
+          <t>https://artportalen.se/Sighting/135512295</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135602165</v>
+        <v>135513277</v>
       </c>
       <c r="B17" t="n">
-        <v>92167</v>
+        <v>101424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751313</v>
+        <v>751608</v>
       </c>
       <c r="R17" t="n">
-        <v>7376133</v>
+        <v>7375832</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2285,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2306,16 +2316,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602165</t>
+          <t>https://artportalen.se/Sighting/135513277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135512444</v>
+        <v>135513622</v>
       </c>
       <c r="B18" t="n">
-        <v>96678</v>
+        <v>101424</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2166</v>
+        <v>1365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751407</v>
+        <v>751666</v>
       </c>
       <c r="R18" t="n">
-        <v>7375917</v>
+        <v>7375784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,16 +2418,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512444</t>
+          <t>https://artportalen.se/Sighting/135513622</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135493935</v>
+        <v>135670886</v>
       </c>
       <c r="B19" t="n">
-        <v>97308</v>
+        <v>101424</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751725</v>
+        <v>751434</v>
       </c>
       <c r="R19" t="n">
-        <v>7375905</v>
+        <v>7375954</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,12 +2489,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2510,16 +2520,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493935</t>
+          <t>https://artportalen.se/Sighting/135670886</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135494039</v>
+        <v>135671019</v>
       </c>
       <c r="B20" t="n">
-        <v>97308</v>
+        <v>101424</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751706</v>
+        <v>751415</v>
       </c>
       <c r="R20" t="n">
-        <v>7375893</v>
+        <v>7375967</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,12 +2591,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2612,38 +2622,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494039</t>
+          <t>https://artportalen.se/Sighting/135671019</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135602205</v>
+        <v>135602165</v>
       </c>
       <c r="B21" t="n">
-        <v>97308</v>
+        <v>92209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751335</v>
+        <v>751313</v>
       </c>
       <c r="R21" t="n">
-        <v>7376158</v>
+        <v>7376133</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2714,38 +2724,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602205</t>
+          <t>https://artportalen.se/Sighting/135602165</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135487454</v>
+        <v>135512444</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>96722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2166</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751385</v>
+        <v>751407</v>
       </c>
       <c r="R22" t="n">
-        <v>7376134</v>
+        <v>7375917</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2795,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,38 +2826,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487454</t>
+          <t>https://artportalen.se/Sighting/135512444</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135487819</v>
+        <v>135493935</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>97352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751340</v>
+        <v>751725</v>
       </c>
       <c r="R23" t="n">
-        <v>7376092</v>
+        <v>7375905</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,38 +2928,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487819</t>
+          <t>https://artportalen.se/Sighting/135493935</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135488053</v>
+        <v>135494039</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>97352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751340</v>
+        <v>751706</v>
       </c>
       <c r="R24" t="n">
-        <v>7376082</v>
+        <v>7375893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,54 +3030,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488053</t>
+          <t>https://artportalen.se/Sighting/135494039</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135488602</v>
+        <v>135602205</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>97352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751370</v>
+        <v>751335</v>
       </c>
       <c r="R25" t="n">
-        <v>7376029</v>
+        <v>7376158</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3091,12 +3101,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3122,16 +3132,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488602</t>
+          <t>https://artportalen.se/Sighting/135602205</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135488683</v>
+        <v>135487454</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751337</v>
+        <v>751385</v>
       </c>
       <c r="R26" t="n">
-        <v>7376020</v>
+        <v>7376134</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,16 +3234,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488683</t>
+          <t>https://artportalen.se/Sighting/135487454</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135510447</v>
+        <v>135487819</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751269</v>
+        <v>751340</v>
       </c>
       <c r="R27" t="n">
-        <v>7375976</v>
+        <v>7376092</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3295,12 +3305,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3326,16 +3336,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510447</t>
+          <t>https://artportalen.se/Sighting/135487819</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135567074</v>
+        <v>135488053</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751757</v>
+        <v>751340</v>
       </c>
       <c r="R28" t="n">
-        <v>7375888</v>
+        <v>7376082</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,12 +3407,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3428,16 +3438,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135567074</t>
+          <t>https://artportalen.se/Sighting/135488053</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135602198</v>
+        <v>135488602</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,17 +3475,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>751306</v>
+        <v>751370</v>
       </c>
       <c r="R29" t="n">
-        <v>7376118</v>
+        <v>7376029</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3499,12 +3509,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3530,38 +3540,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602198</t>
+          <t>https://artportalen.se/Sighting/135488602</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135493576</v>
+        <v>135488683</v>
       </c>
       <c r="B30" t="n">
-        <v>79397</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751658</v>
+        <v>751337</v>
       </c>
       <c r="R30" t="n">
-        <v>7376014</v>
+        <v>7376020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,38 +3642,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493576</t>
+          <t>https://artportalen.se/Sighting/135488683</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135493529</v>
+        <v>135510447</v>
       </c>
       <c r="B31" t="n">
-        <v>80492</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751644</v>
+        <v>751269</v>
       </c>
       <c r="R31" t="n">
-        <v>7376014</v>
+        <v>7375976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3703,12 +3713,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3734,38 +3744,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493529</t>
+          <t>https://artportalen.se/Sighting/135510447</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135513861</v>
+        <v>135567074</v>
       </c>
       <c r="B32" t="n">
-        <v>80492</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751610</v>
+        <v>751757</v>
       </c>
       <c r="R32" t="n">
-        <v>7375777</v>
+        <v>7375888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,12 +3815,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3836,54 +3846,54 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513861</t>
+          <t>https://artportalen.se/Sighting/135567074</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135511907</v>
+        <v>135602198</v>
       </c>
       <c r="B33" t="n">
-        <v>80500</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751338</v>
+        <v>751306</v>
       </c>
       <c r="R33" t="n">
-        <v>7375957</v>
+        <v>7376118</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3907,12 +3917,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3938,16 +3948,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511907</t>
+          <t>https://artportalen.se/Sighting/135602198</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135490400</v>
+        <v>135493576</v>
       </c>
       <c r="B34" t="n">
-        <v>57972</v>
+        <v>79435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3955,21 +3965,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751358</v>
+        <v>751658</v>
       </c>
       <c r="R34" t="n">
-        <v>7376019</v>
+        <v>7376014</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,11 +4027,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4045,38 +4050,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135490400</t>
+          <t>https://artportalen.se/Sighting/135493576</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135487949</v>
+        <v>135493529</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>80530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,10 +4091,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751338</v>
+        <v>751644</v>
       </c>
       <c r="R35" t="n">
-        <v>7376087</v>
+        <v>7376014</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,11 +4129,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack 1</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4152,56 +4152,51 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487949</t>
+          <t>https://artportalen.se/Sighting/135493529</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135492288</v>
+        <v>135513861</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>80530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751533</v>
+        <v>751610</v>
       </c>
       <c r="R36" t="n">
-        <v>7376077</v>
+        <v>7375777</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,17 +4223,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4264,38 +4254,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492288</t>
+          <t>https://artportalen.se/Sighting/135513861</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135492904</v>
+        <v>135511907</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>80538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751604</v>
+        <v>751338</v>
       </c>
       <c r="R37" t="n">
-        <v>7376073</v>
+        <v>7375957</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4335,17 +4325,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4371,33 +4356,33 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492904</t>
+          <t>https://artportalen.se/Sighting/135511907</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135508817</v>
+        <v>135490400</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4406,21 +4391,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751185</v>
+        <v>751358</v>
       </c>
       <c r="R38" t="n">
-        <v>7375925</v>
+        <v>7376019</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,17 +4427,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4483,38 +4463,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508817</t>
+          <t>https://artportalen.se/Sighting/135490400</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135508144</v>
+        <v>135487949</v>
       </c>
       <c r="B39" t="n">
-        <v>5181</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751233</v>
+        <v>751338</v>
       </c>
       <c r="R39" t="n">
-        <v>7375939</v>
+        <v>7376087</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,17 +4534,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4590,51 +4570,56 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508144</t>
+          <t>https://artportalen.se/Sighting/135487949</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135511007</v>
+        <v>135492288</v>
       </c>
       <c r="B40" t="n">
-        <v>12373</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751283</v>
+        <v>751533</v>
       </c>
       <c r="R40" t="n">
-        <v>7375962</v>
+        <v>7376077</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,17 +4646,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4697,38 +4682,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511007</t>
+          <t>https://artportalen.se/Sighting/135492288</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135566886</v>
+        <v>135492904</v>
       </c>
       <c r="B41" t="n">
-        <v>12373</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4738,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751705</v>
+        <v>751604</v>
       </c>
       <c r="R41" t="n">
-        <v>7375824</v>
+        <v>7376073</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4768,17 +4753,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4804,48 +4789,44 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135566886</t>
+          <t>https://artportalen.se/Sighting/135492904</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135508608</v>
+        <v>135508817</v>
       </c>
       <c r="B42" t="n">
-        <v>12573</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101691</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4854,10 +4835,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751209</v>
+        <v>751185</v>
       </c>
       <c r="R42" t="n">
-        <v>7375929</v>
+        <v>7375925</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4892,6 +4873,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4915,38 +4901,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508608</t>
+          <t>https://artportalen.se/Sighting/135508817</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135514248</v>
+        <v>135508144</v>
       </c>
       <c r="B43" t="n">
-        <v>12573</v>
+        <v>5181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101691</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4956,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751562</v>
+        <v>751233</v>
       </c>
       <c r="R43" t="n">
-        <v>7375703</v>
+        <v>7375939</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4994,6 +4980,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5017,54 +5008,54 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135514248</t>
+          <t>https://artportalen.se/Sighting/135508144</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135571094</v>
+        <v>135511007</v>
       </c>
       <c r="B44" t="n">
-        <v>5180</v>
+        <v>12375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102204</v>
+        <v>101283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751322</v>
+        <v>751283</v>
       </c>
       <c r="R44" t="n">
-        <v>7375956</v>
+        <v>7375962</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5098,7 +5089,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5124,63 +5115,54 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135571094</t>
+          <t>https://artportalen.se/Sighting/135511007</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135488308</v>
+        <v>135566886</v>
       </c>
       <c r="B45" t="n">
-        <v>58136</v>
+        <v>12375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>101283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751354</v>
+        <v>751705</v>
       </c>
       <c r="R45" t="n">
-        <v>7376070</v>
+        <v>7375824</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5204,12 +5186,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,54 +5222,63 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488308</t>
+          <t>https://artportalen.se/Sighting/135566886</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135493284</v>
+        <v>135508608</v>
       </c>
       <c r="B46" t="n">
-        <v>58136</v>
+        <v>12575</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751617</v>
+        <v>751209</v>
       </c>
       <c r="R46" t="n">
-        <v>7376065</v>
+        <v>7375929</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5306,12 +5302,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5337,58 +5333,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493284</t>
+          <t>https://artportalen.se/Sighting/135508608</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135487574</v>
+        <v>135514248</v>
       </c>
       <c r="B47" t="n">
-        <v>58678</v>
+        <v>12575</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103056</v>
+        <v>101691</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751357</v>
+        <v>751562</v>
       </c>
       <c r="R47" t="n">
-        <v>7376129</v>
+        <v>7375703</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5412,17 +5404,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ett par i lämplig häckningsbiotop</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,54 +5435,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487574</t>
+          <t>https://artportalen.se/Sighting/135514248</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135491874</v>
+        <v>135571094</v>
       </c>
       <c r="B48" t="n">
-        <v>5201</v>
+        <v>5180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751383</v>
+        <v>751322</v>
       </c>
       <c r="R48" t="n">
-        <v>7376129</v>
+        <v>7375956</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5519,17 +5506,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5555,16 +5542,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491874</t>
+          <t>https://artportalen.se/Sighting/135571094</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135508160</v>
+        <v>135671375</v>
       </c>
       <c r="B49" t="n">
-        <v>5201</v>
+        <v>57158</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5572,16 +5559,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5589,20 +5576,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751232</v>
+        <v>751427</v>
       </c>
       <c r="R49" t="n">
-        <v>7375940</v>
+        <v>7376032</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5626,17 +5622,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5662,16 +5653,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508160</t>
+          <t>https://artportalen.se/Sighting/135671375</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135487999</v>
+        <v>135672510</v>
       </c>
       <c r="B50" t="n">
-        <v>8449</v>
+        <v>57158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5679,21 +5670,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106554</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5703,13 +5694,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751338</v>
+        <v>751439</v>
       </c>
       <c r="R50" t="n">
-        <v>7376085</v>
+        <v>7376095</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5733,17 +5724,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5769,54 +5755,63 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487999</t>
+          <t>https://artportalen.se/Sighting/135672510</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135487698</v>
+        <v>135488308</v>
       </c>
       <c r="B51" t="n">
-        <v>98219</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751357</v>
+        <v>751354</v>
       </c>
       <c r="R51" t="n">
-        <v>7376116</v>
+        <v>7376070</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5871,38 +5866,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135488308</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135493447</v>
+        <v>135493284</v>
       </c>
       <c r="B52" t="n">
-        <v>108205</v>
+        <v>58141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220083</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5912,13 +5907,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751609</v>
+        <v>751617</v>
       </c>
       <c r="R52" t="n">
-        <v>7376039</v>
+        <v>7376065</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5973,38 +5968,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135493284</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135511789</v>
+        <v>135672524</v>
       </c>
       <c r="B53" t="n">
-        <v>108205</v>
+        <v>58141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220083</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6014,13 +6009,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751333</v>
+        <v>751438</v>
       </c>
       <c r="R53" t="n">
-        <v>7375966</v>
+        <v>7376096</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6044,12 +6039,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6075,16 +6070,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135672524</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135487495</v>
+        <v>135487574</v>
       </c>
       <c r="B54" t="n">
-        <v>111153</v>
+        <v>58683</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6092,37 +6087,41 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220240</v>
+        <v>103056</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751361</v>
+        <v>751357</v>
       </c>
       <c r="R54" t="n">
-        <v>7376128</v>
+        <v>7376129</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6152,6 +6151,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ett par i lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6177,16 +6181,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135487574</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135492620</v>
+        <v>135491874</v>
       </c>
       <c r="B55" t="n">
-        <v>111153</v>
+        <v>5201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6194,21 +6198,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220240</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6218,10 +6222,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751566</v>
+        <v>751383</v>
       </c>
       <c r="R55" t="n">
-        <v>7376059</v>
+        <v>7376129</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6256,6 +6260,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6279,16 +6288,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135491874</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135512174</v>
+        <v>135508160</v>
       </c>
       <c r="B56" t="n">
-        <v>111153</v>
+        <v>5201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6296,21 +6305,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220240</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6320,7 +6329,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751350</v>
+        <v>751232</v>
       </c>
       <c r="R56" t="n">
         <v>7375940</v>
@@ -6358,6 +6367,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6381,38 +6395,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135508160</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135488283</v>
+        <v>135487999</v>
       </c>
       <c r="B57" t="n">
-        <v>99195</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6425,7 +6439,7 @@
         <v>751338</v>
       </c>
       <c r="R57" t="n">
-        <v>7376087</v>
+        <v>7376085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6462,7 +6476,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Växtplats 1</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6488,16 +6502,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135487999</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135492603</v>
+        <v>135670489</v>
       </c>
       <c r="B58" t="n">
-        <v>99195</v>
+        <v>43388</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6505,21 +6519,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>201075</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6529,10 +6543,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>751552</v>
+        <v>751510</v>
       </c>
       <c r="R58" t="n">
-        <v>7376059</v>
+        <v>7375874</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,12 +6573,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6590,16 +6604,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135670489</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135510422</v>
+        <v>135669405</v>
       </c>
       <c r="B59" t="n">
-        <v>106309</v>
+        <v>58844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6607,21 +6621,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>208249</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6631,10 +6645,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>751264</v>
+        <v>751402</v>
       </c>
       <c r="R59" t="n">
-        <v>7375973</v>
+        <v>7375948</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6661,12 +6675,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6692,16 +6706,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135487671</v>
+        <v>135487698</v>
       </c>
       <c r="B60" t="n">
-        <v>98060</v>
+        <v>98263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6709,21 +6723,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>219815</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6733,10 +6747,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751354</v>
+        <v>751357</v>
       </c>
       <c r="R60" t="n">
-        <v>7376126</v>
+        <v>7376116</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6794,16 +6808,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135488071</v>
+        <v>135493447</v>
       </c>
       <c r="B61" t="n">
-        <v>99217</v>
+        <v>108260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6811,21 +6825,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220083</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6835,10 +6849,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751342</v>
+        <v>751609</v>
       </c>
       <c r="R61" t="n">
-        <v>7376081</v>
+        <v>7376039</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6896,16 +6910,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135511436</v>
+        <v>135511789</v>
       </c>
       <c r="B62" t="n">
-        <v>99001</v>
+        <v>108260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6913,21 +6927,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223049</v>
+        <v>220083</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6937,10 +6951,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>751315</v>
+        <v>751333</v>
       </c>
       <c r="R62" t="n">
-        <v>7375971</v>
+        <v>7375966</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6998,16 +7012,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135491240</v>
+        <v>135487495</v>
       </c>
       <c r="B63" t="n">
-        <v>98249</v>
+        <v>111210</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7015,21 +7029,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223358</v>
+        <v>220240</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7039,10 +7053,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751305</v>
+        <v>751361</v>
       </c>
       <c r="R63" t="n">
-        <v>7376101</v>
+        <v>7376128</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7100,54 +7114,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135602173</v>
+        <v>135492620</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>111210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>260591</v>
+        <v>220240</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751327</v>
+        <v>751566</v>
       </c>
       <c r="R64" t="n">
-        <v>7376136</v>
+        <v>7376059</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7171,17 +7185,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7206,6 +7215,1036 @@
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492620</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135512174</v>
+      </c>
+      <c r="B65" t="n">
+        <v>111210</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>751350</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7375940</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512174</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135488283</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488283</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135492603</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>751552</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492603</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135510422</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106364</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>751264</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7375973</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510422</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135487671</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7376126</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487671</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99264</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488071</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99048</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511436</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135670818</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99048</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>751435</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7375942</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135670818</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98293</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79434</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -7276,6 +8315,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ74"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>99240</v>
+        <v>99267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135511669</v>
       </c>
       <c r="B9" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79950</v>
+        <v>79977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,48 +1710,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135494092</v>
+        <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>101424</v>
+        <v>79977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1365</v>
+        <v>1353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751697</v>
+        <v>751301</v>
       </c>
       <c r="R12" t="n">
-        <v>7375888</v>
+        <v>7376014</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1775,12 +1775,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1806,16 +1811,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494092</t>
+          <t>https://artportalen.se/Sighting/135675709</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135494212</v>
+        <v>135494092</v>
       </c>
       <c r="B13" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751690</v>
+        <v>751697</v>
       </c>
       <c r="R13" t="n">
-        <v>7375884</v>
+        <v>7375888</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,16 +1913,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494212</t>
+          <t>https://artportalen.se/Sighting/135494092</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135494377</v>
+        <v>135494212</v>
       </c>
       <c r="B14" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751681</v>
+        <v>751690</v>
       </c>
       <c r="R14" t="n">
-        <v>7375876</v>
+        <v>7375884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,16 +2015,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494377</t>
+          <t>https://artportalen.se/Sighting/135494212</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135494485</v>
+        <v>135494377</v>
       </c>
       <c r="B15" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751677</v>
+        <v>751681</v>
       </c>
       <c r="R15" t="n">
-        <v>7375866</v>
+        <v>7375876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,16 +2117,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494485</t>
+          <t>https://artportalen.se/Sighting/135494377</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135512295</v>
+        <v>135494485</v>
       </c>
       <c r="B16" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751362</v>
+        <v>751677</v>
       </c>
       <c r="R16" t="n">
-        <v>7375922</v>
+        <v>7375866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,12 +2188,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,16 +2219,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512295</t>
+          <t>https://artportalen.se/Sighting/135494485</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135513277</v>
+        <v>135512295</v>
       </c>
       <c r="B17" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751608</v>
+        <v>751362</v>
       </c>
       <c r="R17" t="n">
-        <v>7375832</v>
+        <v>7375922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,16 +2321,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513277</t>
+          <t>https://artportalen.se/Sighting/135512295</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135513622</v>
+        <v>135513277</v>
       </c>
       <c r="B18" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751666</v>
+        <v>751608</v>
       </c>
       <c r="R18" t="n">
-        <v>7375784</v>
+        <v>7375832</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,16 +2423,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513622</t>
+          <t>https://artportalen.se/Sighting/135513277</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135670886</v>
+        <v>135513622</v>
       </c>
       <c r="B19" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751434</v>
+        <v>751666</v>
       </c>
       <c r="R19" t="n">
-        <v>7375954</v>
+        <v>7375784</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,12 +2494,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,16 +2525,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670886</t>
+          <t>https://artportalen.se/Sighting/135513622</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135671019</v>
+        <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101424</v>
+        <v>101451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751415</v>
+        <v>751434</v>
       </c>
       <c r="R20" t="n">
-        <v>7375967</v>
+        <v>7375954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,54 +2627,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135671019</t>
+          <t>https://artportalen.se/Sighting/135670886</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135602165</v>
+        <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>92209</v>
+        <v>101451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751313</v>
+        <v>751415</v>
       </c>
       <c r="R21" t="n">
-        <v>7376133</v>
+        <v>7375967</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2693,12 +2698,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,16 +2729,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602165</t>
+          <t>https://artportalen.se/Sighting/135671019</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135512444</v>
+        <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>96722</v>
+        <v>101451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,37 +2746,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2166</v>
+        <v>1365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751407</v>
+        <v>751416</v>
       </c>
       <c r="R22" t="n">
-        <v>7375917</v>
+        <v>7375966</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2795,12 +2800,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2826,16 +2831,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512444</t>
+          <t>https://artportalen.se/Sighting/135675710</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135493935</v>
+        <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>97352</v>
+        <v>101451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,37 +2848,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751725</v>
+        <v>751432</v>
       </c>
       <c r="R23" t="n">
-        <v>7375905</v>
+        <v>7375958</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2897,12 +2902,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2928,16 +2933,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493935</t>
+          <t>https://artportalen.se/Sighting/135675711</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135494039</v>
+        <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>97352</v>
+        <v>101451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,37 +2950,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751706</v>
+        <v>751406</v>
       </c>
       <c r="R24" t="n">
-        <v>7375893</v>
+        <v>7375984</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2999,12 +3004,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,16 +3035,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135494039</t>
+          <t>https://artportalen.se/Sighting/135675712</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135602205</v>
+        <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>97352</v>
+        <v>101451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3047,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751335</v>
+        <v>751415</v>
       </c>
       <c r="R25" t="n">
-        <v>7376158</v>
+        <v>7375974</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3101,12 +3106,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3132,54 +3137,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602205</t>
+          <t>https://artportalen.se/Sighting/135675713</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135487454</v>
+        <v>135602165</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>92236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751385</v>
+        <v>751313</v>
       </c>
       <c r="R26" t="n">
-        <v>7376134</v>
+        <v>7376133</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3203,12 +3208,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3234,38 +3239,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487454</t>
+          <t>https://artportalen.se/Sighting/135602165</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135487819</v>
+        <v>135512444</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>96749</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2166</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>751340</v>
+        <v>751407</v>
       </c>
       <c r="R27" t="n">
-        <v>7376092</v>
+        <v>7375917</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,12 +3310,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3336,38 +3341,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487819</t>
+          <t>https://artportalen.se/Sighting/135512444</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135488053</v>
+        <v>135493935</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>97379</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>751340</v>
+        <v>751725</v>
       </c>
       <c r="R28" t="n">
-        <v>7376082</v>
+        <v>7375905</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,38 +3443,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488053</t>
+          <t>https://artportalen.se/Sighting/135493935</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135488602</v>
+        <v>135494039</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>97379</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>751370</v>
+        <v>751706</v>
       </c>
       <c r="R29" t="n">
-        <v>7376029</v>
+        <v>7375893</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,54 +3545,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488602</t>
+          <t>https://artportalen.se/Sighting/135494039</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135488683</v>
+        <v>135602205</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>97379</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751337</v>
+        <v>751335</v>
       </c>
       <c r="R30" t="n">
-        <v>7376020</v>
+        <v>7376158</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3611,12 +3616,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3642,16 +3647,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488683</t>
+          <t>https://artportalen.se/Sighting/135602205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135510447</v>
+        <v>135487454</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3683,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751269</v>
+        <v>751385</v>
       </c>
       <c r="R31" t="n">
-        <v>7375976</v>
+        <v>7376134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,12 +3718,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3744,16 +3749,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510447</t>
+          <t>https://artportalen.se/Sighting/135487454</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135567074</v>
+        <v>135487819</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3785,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751757</v>
+        <v>751340</v>
       </c>
       <c r="R32" t="n">
-        <v>7375888</v>
+        <v>7376092</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3815,12 +3820,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3846,16 +3851,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135567074</t>
+          <t>https://artportalen.se/Sighting/135487819</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135602198</v>
+        <v>135488053</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3883,17 +3888,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751306</v>
+        <v>751340</v>
       </c>
       <c r="R33" t="n">
-        <v>7376118</v>
+        <v>7376082</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3917,12 +3922,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3948,38 +3953,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135602198</t>
+          <t>https://artportalen.se/Sighting/135488053</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135493576</v>
+        <v>135488602</v>
       </c>
       <c r="B34" t="n">
-        <v>79435</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751658</v>
+        <v>751370</v>
       </c>
       <c r="R34" t="n">
-        <v>7376014</v>
+        <v>7376029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,38 +4055,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493576</t>
+          <t>https://artportalen.se/Sighting/135488602</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135493529</v>
+        <v>135488683</v>
       </c>
       <c r="B35" t="n">
-        <v>80530</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751644</v>
+        <v>751337</v>
       </c>
       <c r="R35" t="n">
-        <v>7376014</v>
+        <v>7376020</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,38 +4157,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493529</t>
+          <t>https://artportalen.se/Sighting/135488683</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135513861</v>
+        <v>135510447</v>
       </c>
       <c r="B36" t="n">
-        <v>80530</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751610</v>
+        <v>751269</v>
       </c>
       <c r="R36" t="n">
-        <v>7375777</v>
+        <v>7375976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,38 +4259,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135513861</t>
+          <t>https://artportalen.se/Sighting/135510447</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135511907</v>
+        <v>135567074</v>
       </c>
       <c r="B37" t="n">
-        <v>80538</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751338</v>
+        <v>751757</v>
       </c>
       <c r="R37" t="n">
-        <v>7375957</v>
+        <v>7375888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,12 +4330,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4356,54 +4361,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511907</t>
+          <t>https://artportalen.se/Sighting/135567074</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135490400</v>
+        <v>135602198</v>
       </c>
       <c r="B38" t="n">
-        <v>57977</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751358</v>
+        <v>751306</v>
       </c>
       <c r="R38" t="n">
-        <v>7376019</v>
+        <v>7376118</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4427,17 +4432,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4463,38 +4463,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135490400</t>
+          <t>https://artportalen.se/Sighting/135602198</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135487949</v>
+        <v>135493576</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>79462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751338</v>
+        <v>751658</v>
       </c>
       <c r="R39" t="n">
-        <v>7376087</v>
+        <v>7376014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,11 +4542,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack 1</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4570,56 +4565,51 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487949</t>
+          <t>https://artportalen.se/Sighting/135493576</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135492288</v>
+        <v>135493529</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>80557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751533</v>
+        <v>751644</v>
       </c>
       <c r="R40" t="n">
-        <v>7376077</v>
+        <v>7376014</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4654,11 +4644,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4682,38 +4667,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492288</t>
+          <t>https://artportalen.se/Sighting/135493529</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135492904</v>
+        <v>135513861</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>80557</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751604</v>
+        <v>751610</v>
       </c>
       <c r="R41" t="n">
-        <v>7376073</v>
+        <v>7375777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,17 +4738,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4789,56 +4769,51 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492904</t>
+          <t>https://artportalen.se/Sighting/135513861</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135508817</v>
+        <v>135511907</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>80565</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751185</v>
+        <v>751338</v>
       </c>
       <c r="R42" t="n">
-        <v>7375925</v>
+        <v>7375957</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4873,11 +4848,6 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4901,16 +4871,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508817</t>
+          <t>https://artportalen.se/Sighting/135511907</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135508144</v>
+        <v>135490400</v>
       </c>
       <c r="B43" t="n">
-        <v>5181</v>
+        <v>57977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4918,21 +4888,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4942,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751233</v>
+        <v>751358</v>
       </c>
       <c r="R43" t="n">
-        <v>7375939</v>
+        <v>7376019</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4972,17 +4942,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5008,38 +4978,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508144</t>
+          <t>https://artportalen.se/Sighting/135490400</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135511007</v>
+        <v>135487949</v>
       </c>
       <c r="B44" t="n">
-        <v>12375</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5049,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751283</v>
+        <v>751338</v>
       </c>
       <c r="R44" t="n">
-        <v>7375962</v>
+        <v>7376087</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,17 +5049,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+          <t>Ringhack 1</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5115,51 +5085,56 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511007</t>
+          <t>https://artportalen.se/Sighting/135487949</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135566886</v>
+        <v>135492288</v>
       </c>
       <c r="B45" t="n">
-        <v>12375</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>101283</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751705</v>
+        <v>751533</v>
       </c>
       <c r="R45" t="n">
-        <v>7375824</v>
+        <v>7376077</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,17 +5161,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5222,60 +5197,51 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135566886</t>
+          <t>https://artportalen.se/Sighting/135492288</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135508608</v>
+        <v>135492904</v>
       </c>
       <c r="B46" t="n">
-        <v>12575</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101691</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751209</v>
+        <v>751604</v>
       </c>
       <c r="R46" t="n">
-        <v>7375929</v>
+        <v>7376073</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,12 +5268,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5333,51 +5304,56 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508608</t>
+          <t>https://artportalen.se/Sighting/135492904</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135514248</v>
+        <v>135508817</v>
       </c>
       <c r="B47" t="n">
-        <v>12575</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101691</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre barkplattbagge</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pytho abieticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>J.Sahlberg, 1875</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751562</v>
+        <v>751185</v>
       </c>
       <c r="R47" t="n">
-        <v>7375703</v>
+        <v>7375925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5412,6 +5388,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5435,54 +5416,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135514248</t>
+          <t>https://artportalen.se/Sighting/135508817</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135571094</v>
+        <v>135508144</v>
       </c>
       <c r="B48" t="n">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751322</v>
+        <v>751233</v>
       </c>
       <c r="R48" t="n">
-        <v>7375956</v>
+        <v>7375939</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5516,7 +5497,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5542,63 +5523,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135571094</t>
+          <t>https://artportalen.se/Sighting/135508144</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135671375</v>
+        <v>135511007</v>
       </c>
       <c r="B49" t="n">
-        <v>57158</v>
+        <v>12375</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>101283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751427</v>
+        <v>751283</v>
       </c>
       <c r="R49" t="n">
-        <v>7376032</v>
+        <v>7375962</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5622,12 +5594,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5653,38 +5630,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135671375</t>
+          <t>https://artportalen.se/Sighting/135511007</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135672510</v>
+        <v>135566886</v>
       </c>
       <c r="B50" t="n">
-        <v>57158</v>
+        <v>12375</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>101283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5694,13 +5671,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751439</v>
+        <v>751705</v>
       </c>
       <c r="R50" t="n">
-        <v>7376095</v>
+        <v>7375824</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5724,12 +5701,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5755,38 +5737,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672510</t>
+          <t>https://artportalen.se/Sighting/135566886</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135488308</v>
+        <v>135508608</v>
       </c>
       <c r="B51" t="n">
-        <v>58141</v>
+        <v>12575</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5796,7 +5778,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>larv/nymf</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5805,13 +5787,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751354</v>
+        <v>751209</v>
       </c>
       <c r="R51" t="n">
-        <v>7376070</v>
+        <v>7375929</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5835,12 +5817,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5866,38 +5848,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488308</t>
+          <t>https://artportalen.se/Sighting/135508608</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135493284</v>
+        <v>135514248</v>
       </c>
       <c r="B52" t="n">
-        <v>58141</v>
+        <v>12575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>101691</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre barkplattbagge</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pytho abieticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.Sahlberg, 1875</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5907,13 +5889,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>751617</v>
+        <v>751562</v>
       </c>
       <c r="R52" t="n">
-        <v>7376065</v>
+        <v>7375703</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5937,12 +5919,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5968,16 +5950,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493284</t>
+          <t>https://artportalen.se/Sighting/135514248</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135672524</v>
+        <v>135571094</v>
       </c>
       <c r="B53" t="n">
-        <v>58141</v>
+        <v>5180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5985,34 +5967,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>751438</v>
+        <v>751322</v>
       </c>
       <c r="R53" t="n">
-        <v>7376096</v>
+        <v>7375956</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6039,12 +6021,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6070,16 +6057,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135672524</t>
+          <t>https://artportalen.se/Sighting/135571094</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135487574</v>
+        <v>135671375</v>
       </c>
       <c r="B54" t="n">
-        <v>58683</v>
+        <v>57158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6087,21 +6074,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103056</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6109,19 +6096,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>751357</v>
+        <v>751427</v>
       </c>
       <c r="R54" t="n">
-        <v>7376129</v>
+        <v>7376032</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6145,17 +6137,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ett par i lämplig häckningsbiotop</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6181,16 +6168,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487574</t>
+          <t>https://artportalen.se/Sighting/135671375</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135491874</v>
+        <v>135672510</v>
       </c>
       <c r="B55" t="n">
-        <v>5201</v>
+        <v>57158</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6198,16 +6185,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6222,13 +6209,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>751383</v>
+        <v>751439</v>
       </c>
       <c r="R55" t="n">
-        <v>7376129</v>
+        <v>7376095</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6252,17 +6239,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6288,54 +6270,63 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491874</t>
+          <t>https://artportalen.se/Sighting/135672510</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135508160</v>
+        <v>135488308</v>
       </c>
       <c r="B56" t="n">
-        <v>5201</v>
+        <v>58141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>751232</v>
+        <v>751354</v>
       </c>
       <c r="R56" t="n">
-        <v>7375940</v>
+        <v>7376070</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6359,17 +6350,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6395,38 +6381,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135508160</t>
+          <t>https://artportalen.se/Sighting/135488308</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135487999</v>
+        <v>135493284</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>58141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6436,13 +6422,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>751338</v>
+        <v>751617</v>
       </c>
       <c r="R57" t="n">
-        <v>7376085</v>
+        <v>7376065</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6472,11 +6458,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6502,38 +6483,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487999</t>
+          <t>https://artportalen.se/Sighting/135493284</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135670489</v>
+        <v>135672524</v>
       </c>
       <c r="B58" t="n">
-        <v>43388</v>
+        <v>58141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>201075</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6543,13 +6524,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>751510</v>
+        <v>751438</v>
       </c>
       <c r="R58" t="n">
-        <v>7375874</v>
+        <v>7376096</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6604,16 +6585,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670489</t>
+          <t>https://artportalen.se/Sighting/135672524</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135669405</v>
+        <v>135487574</v>
       </c>
       <c r="B59" t="n">
-        <v>58844</v>
+        <v>58683</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6621,37 +6602,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>208249</v>
+        <v>103056</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>751402</v>
+        <v>751357</v>
       </c>
       <c r="R59" t="n">
-        <v>7375948</v>
+        <v>7376129</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6675,12 +6660,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ett par i lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6706,16 +6696,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135487574</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135487698</v>
+        <v>135491874</v>
       </c>
       <c r="B60" t="n">
-        <v>98263</v>
+        <v>5201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6723,21 +6713,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219815</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6747,10 +6737,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>751357</v>
+        <v>751383</v>
       </c>
       <c r="R60" t="n">
-        <v>7376116</v>
+        <v>7376129</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6785,6 +6775,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6808,16 +6803,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135491874</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135493447</v>
+        <v>135508160</v>
       </c>
       <c r="B61" t="n">
-        <v>108260</v>
+        <v>5201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6825,21 +6820,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220083</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6849,10 +6844,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>751609</v>
+        <v>751232</v>
       </c>
       <c r="R61" t="n">
-        <v>7376039</v>
+        <v>7375940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6879,12 +6874,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6910,16 +6910,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135508160</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135511789</v>
+        <v>135487999</v>
       </c>
       <c r="B62" t="n">
-        <v>108260</v>
+        <v>8450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6927,21 +6927,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220083</v>
+        <v>106554</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>751333</v>
+        <v>751338</v>
       </c>
       <c r="R62" t="n">
-        <v>7375966</v>
+        <v>7376085</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6981,12 +6981,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7012,16 +7017,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135487999</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135487495</v>
+        <v>135669405</v>
       </c>
       <c r="B63" t="n">
-        <v>111210</v>
+        <v>58844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7029,21 +7034,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220240</v>
+        <v>208249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7053,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751361</v>
+        <v>751402</v>
       </c>
       <c r="R63" t="n">
-        <v>7376128</v>
+        <v>7375948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7083,12 +7088,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7114,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135492620</v>
+        <v>135487698</v>
       </c>
       <c r="B64" t="n">
-        <v>111210</v>
+        <v>98290</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7131,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220240</v>
+        <v>219815</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7155,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751566</v>
+        <v>751357</v>
       </c>
       <c r="R64" t="n">
-        <v>7376059</v>
+        <v>7376116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7216,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135512174</v>
+        <v>135493447</v>
       </c>
       <c r="B65" t="n">
-        <v>111210</v>
+        <v>108287</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7233,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7257,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751350</v>
+        <v>751609</v>
       </c>
       <c r="R65" t="n">
-        <v>7375940</v>
+        <v>7376039</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7287,12 +7292,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7318,38 +7323,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135488283</v>
+        <v>135511789</v>
       </c>
       <c r="B66" t="n">
-        <v>99242</v>
+        <v>108287</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7359,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751338</v>
+        <v>751333</v>
       </c>
       <c r="R66" t="n">
-        <v>7376087</v>
+        <v>7375966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,17 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,38 +7425,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135492603</v>
+        <v>135487495</v>
       </c>
       <c r="B67" t="n">
-        <v>99242</v>
+        <v>111237</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751552</v>
+        <v>751361</v>
       </c>
       <c r="R67" t="n">
-        <v>7376059</v>
+        <v>7376128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7527,16 +7527,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135510422</v>
+        <v>135492620</v>
       </c>
       <c r="B68" t="n">
-        <v>106364</v>
+        <v>111237</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7544,21 +7544,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>220240</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751264</v>
+        <v>751566</v>
       </c>
       <c r="R68" t="n">
-        <v>7375973</v>
+        <v>7376059</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7598,12 +7598,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7629,16 +7629,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135487671</v>
+        <v>135512174</v>
       </c>
       <c r="B69" t="n">
-        <v>98104</v>
+        <v>111237</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7646,16 +7646,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220240</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751354</v>
+        <v>751350</v>
       </c>
       <c r="R69" t="n">
-        <v>7376126</v>
+        <v>7375940</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135488071</v>
+        <v>135488283</v>
       </c>
       <c r="B70" t="n">
-        <v>99264</v>
+        <v>99269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751342</v>
+        <v>751338</v>
       </c>
       <c r="R70" t="n">
-        <v>7376081</v>
+        <v>7376087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7810,6 +7810,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7833,38 +7838,38 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135511436</v>
+        <v>135492603</v>
       </c>
       <c r="B71" t="n">
-        <v>99048</v>
+        <v>99269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7874,10 +7879,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751315</v>
+        <v>751552</v>
       </c>
       <c r="R71" t="n">
-        <v>7375971</v>
+        <v>7376059</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7904,12 +7909,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7935,16 +7940,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135670818</v>
+        <v>135510422</v>
       </c>
       <c r="B72" t="n">
-        <v>99048</v>
+        <v>106391</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7952,21 +7957,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223049</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7976,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751435</v>
+        <v>751264</v>
       </c>
       <c r="R72" t="n">
-        <v>7375942</v>
+        <v>7375973</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8006,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8037,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135491240</v>
+        <v>135487671</v>
       </c>
       <c r="B73" t="n">
-        <v>98293</v>
+        <v>98131</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8054,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223358</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8078,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751305</v>
+        <v>751354</v>
       </c>
       <c r="R73" t="n">
-        <v>7376101</v>
+        <v>7376126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8139,54 +8144,54 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135602173</v>
+        <v>135488071</v>
       </c>
       <c r="B74" t="n">
-        <v>79434</v>
+        <v>99291</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751327</v>
+        <v>751342</v>
       </c>
       <c r="R74" t="n">
-        <v>7376136</v>
+        <v>7376081</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8210,17 +8215,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8245,6 +8245,419 @@
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488071</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511436</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135670818</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>751435</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7375942</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135670818</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98320</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79461</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8325,6 +8738,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135669405</v>
+        <v>135670489</v>
       </c>
       <c r="B63" t="n">
-        <v>58844</v>
+        <v>43388</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751402</v>
+        <v>751510</v>
       </c>
       <c r="R63" t="n">
-        <v>7375948</v>
+        <v>7375874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135670489</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135487698</v>
+        <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>98290</v>
+        <v>58844</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219815</v>
+        <v>208249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751357</v>
+        <v>751402</v>
       </c>
       <c r="R64" t="n">
-        <v>7376116</v>
+        <v>7375948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135493447</v>
+        <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>108287</v>
+        <v>98290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751609</v>
+        <v>751357</v>
       </c>
       <c r="R65" t="n">
-        <v>7376039</v>
+        <v>7376116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135511789</v>
+        <v>135493447</v>
       </c>
       <c r="B66" t="n">
         <v>108287</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751333</v>
+        <v>751609</v>
       </c>
       <c r="R66" t="n">
-        <v>7375966</v>
+        <v>7376039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135487495</v>
+        <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>111237</v>
+        <v>108287</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751361</v>
+        <v>751333</v>
       </c>
       <c r="R67" t="n">
-        <v>7376128</v>
+        <v>7375966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135492620</v>
+        <v>135487495</v>
       </c>
       <c r="B68" t="n">
         <v>111237</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751566</v>
+        <v>751361</v>
       </c>
       <c r="R68" t="n">
-        <v>7376059</v>
+        <v>7376128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135512174</v>
+        <v>135492620</v>
       </c>
       <c r="B69" t="n">
         <v>111237</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751350</v>
+        <v>751566</v>
       </c>
       <c r="R69" t="n">
-        <v>7375940</v>
+        <v>7376059</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135488283</v>
+        <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>99269</v>
+        <v>111237</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751338</v>
+        <v>751350</v>
       </c>
       <c r="R70" t="n">
-        <v>7376087</v>
+        <v>7375940</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,17 +7802,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7838,13 +7833,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135492603</v>
+        <v>135488283</v>
       </c>
       <c r="B71" t="n">
         <v>99269</v>
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751552</v>
+        <v>751338</v>
       </c>
       <c r="R71" t="n">
-        <v>7376059</v>
+        <v>7376087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,6 +7912,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135510422</v>
+        <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>106391</v>
+        <v>99269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751264</v>
+        <v>751552</v>
       </c>
       <c r="R72" t="n">
-        <v>7375973</v>
+        <v>7376059</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135487671</v>
+        <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>98131</v>
+        <v>106391</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751354</v>
+        <v>751264</v>
       </c>
       <c r="R73" t="n">
-        <v>7376126</v>
+        <v>7375973</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135488071</v>
+        <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>99291</v>
+        <v>98131</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751342</v>
+        <v>751354</v>
       </c>
       <c r="R74" t="n">
-        <v>7376081</v>
+        <v>7376126</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135511436</v>
+        <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99075</v>
+        <v>99291</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751315</v>
+        <v>751342</v>
       </c>
       <c r="R75" t="n">
-        <v>7375971</v>
+        <v>7376081</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,13 +8348,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135670818</v>
+        <v>135511436</v>
       </c>
       <c r="B76" t="n">
         <v>99075</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751435</v>
+        <v>751315</v>
       </c>
       <c r="R76" t="n">
-        <v>7375942</v>
+        <v>7375971</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135491240</v>
+        <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>98320</v>
+        <v>99075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751305</v>
+        <v>751435</v>
       </c>
       <c r="R77" t="n">
-        <v>7376101</v>
+        <v>7375942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135602173</v>
+        <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>79461</v>
+        <v>98320</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>260591</v>
+        <v>223358</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751327</v>
+        <v>751305</v>
       </c>
       <c r="R78" t="n">
-        <v>7376136</v>
+        <v>7376101</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,17 +8623,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8658,6 +8653,113 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79461</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8742,6 +8844,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91820112</v>
+        <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>99272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751215</v>
+        <v>751279</v>
       </c>
       <c r="R2" t="n">
-        <v>7375871</v>
+        <v>7375962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91820112</t>
+          <t>https://artportalen.se/Sighting/135511421</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91820093</v>
+        <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92369</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751353</v>
+        <v>751297</v>
       </c>
       <c r="R3" t="n">
-        <v>7376123</v>
+        <v>7376037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91820093</t>
+          <t>https://artportalen.se/Sighting/135488970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91820113</v>
+        <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övre Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751208</v>
+        <v>751373</v>
       </c>
       <c r="R4" t="n">
-        <v>7375899</v>
+        <v>7376101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,18 +969,7799 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Falk</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135490783</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135492457</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751543</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7376055</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492457</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>91820112</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79406</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>864</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>751215</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7375871</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820112</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91820093</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>751353</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7376123</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820093</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91820113</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övre Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>751208</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7375899</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-08-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/91820113</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135511669</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>751320</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7375962</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511669</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135668795</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>751275</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7376009</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växtplats 17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135668795</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135671559</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>751426</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7376039</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växtplats 19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135671559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135675709</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1353</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådbrosklav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramalina thrausta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>751301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7376014</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växtplats 18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675709</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135494092</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>751697</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7375888</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494092</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135494212</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>751690</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7375884</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494212</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135494377</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>751681</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7375876</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494377</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135494485</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>751677</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7375866</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494485</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135512295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>751362</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7375922</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512295</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135513277</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>751608</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7375832</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513277</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135513622</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>751666</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7375784</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513622</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135670886</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751434</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7375954</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135670886</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135671019</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>751415</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7375967</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135671019</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135675710</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>751416</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7375966</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675710</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135675711</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>751432</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7375958</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675711</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135675712</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>751406</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7375984</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675712</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135675713</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101456</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>751415</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7375974</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135675713</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135602165</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92241</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>751313</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7376133</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135602165</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135512444</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96754</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skör kvastmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dicranum fragilifolium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Lindb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>751407</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7375917</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512444</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135493935</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97384</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751725</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7375905</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493935</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135494039</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97384</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>751706</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7375893</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135494039</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135602205</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97384</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>751335</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7376158</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135602205</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135487454</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>751385</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7376134</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487454</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135487819</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>751340</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7376092</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487819</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135488053</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>751340</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7376082</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488053</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135488602</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>751370</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7376029</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488602</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135488683</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>751337</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7376020</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488683</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135510447</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>751269</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7375976</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510447</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135567074</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>751757</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7375888</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135567074</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135602198</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>751306</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7376118</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135602198</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135493576</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79465</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>751658</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7376014</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493576</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135493529</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>751644</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7376014</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493529</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135513861</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80560</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>751610</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7375777</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135513861</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135511907</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7375957</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511907</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135490400</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>751358</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7376019</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135490400</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135487949</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack 1</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487949</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135492288</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>751533</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7376077</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492288</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135492904</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>751604</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7376073</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492904</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135508817</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>751185</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7375925</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508817</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135508144</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>751233</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7375939</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508144</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135511007</v>
+      </c>
+      <c r="B49" t="n">
+        <v>12375</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>101283</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Melandrya dubia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>751283</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7375962</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kläckhål i björkhögstubbe samt i låga med fnösktickor.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511007</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135566886</v>
+      </c>
+      <c r="B50" t="n">
+        <v>12375</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>101283</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Melandrya dubia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>751705</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7375824</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kläckhål och svartfärgad larvgång in i vitrötad björkhögstubbe med fnösktickor.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135566886</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135508608</v>
+      </c>
+      <c r="B51" t="n">
+        <v>12575</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>751209</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7375929</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508608</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135514248</v>
+      </c>
+      <c r="B52" t="n">
+        <v>12575</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>101691</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre barkplattbagge</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pytho abieticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>J.Sahlberg, 1875</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>751562</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7375703</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135514248</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135571094</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5180</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>751322</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7375956</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gnagkammare med 5 mm oval gnaggång /kläckhål</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135571094</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135671375</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>751427</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7376032</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135671375</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135672510</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>751439</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7376095</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135672510</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135488308</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7376070</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488308</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135493284</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>751617</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7376065</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493284</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135672524</v>
+      </c>
+      <c r="B58" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>751438</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7376096</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135672524</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135487574</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58683</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ett par i lämplig häckningsbiotop</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487574</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135491874</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>751383</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7376129</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491874</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135508160</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>751232</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7375940</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135508160</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135487999</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7376085</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487999</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135670489</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43388</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>751510</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7375874</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135670489</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135669405</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>751402</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7375948</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135669405</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135487698</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98295</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>751357</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7376116</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487698</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135493447</v>
+      </c>
+      <c r="B66" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>751609</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7376039</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493447</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135511789</v>
+      </c>
+      <c r="B67" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>751333</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7375966</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511789</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135487495</v>
+      </c>
+      <c r="B68" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>751361</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7376128</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487495</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135492620</v>
+      </c>
+      <c r="B69" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>751566</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492620</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135512174</v>
+      </c>
+      <c r="B70" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>751350</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7375940</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135512174</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135488283</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>751338</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7376087</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488283</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135492603</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>751552</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7376059</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492603</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135510422</v>
+      </c>
+      <c r="B73" t="n">
+        <v>106396</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>751264</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7375973</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135510422</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135487671</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>751354</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7376126</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135487671</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135488071</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>751342</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7376081</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135488071</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135511436</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>751315</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7375971</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135511436</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135670818</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>751435</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7375942</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135670818</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135491240</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>751305</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7376101</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135602173</t>
         </is>
       </c>
     </row>
@@ -989,6 +8770,81 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>99272</v>
+        <v>99274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135494092</v>
       </c>
       <c r="B13" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>135494212</v>
       </c>
       <c r="B14" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135494377</v>
       </c>
       <c r="B15" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135494485</v>
       </c>
       <c r="B16" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135512295</v>
       </c>
       <c r="B17" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>135513277</v>
       </c>
       <c r="B18" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135513622</v>
       </c>
       <c r="B19" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101456</v>
+        <v>101458</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135602165</v>
       </c>
       <c r="B26" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135512444</v>
       </c>
       <c r="B27" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135493935</v>
       </c>
       <c r="B28" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135494039</v>
       </c>
       <c r="B29" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135602205</v>
       </c>
       <c r="B30" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>135493447</v>
       </c>
       <c r="B66" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>135487495</v>
       </c>
       <c r="B68" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>135492620</v>
       </c>
       <c r="B69" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>135488283</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>135511436</v>
       </c>
       <c r="B76" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135670489</v>
+        <v>135669405</v>
       </c>
       <c r="B63" t="n">
-        <v>43388</v>
+        <v>58844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>201075</v>
+        <v>208249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751510</v>
+        <v>751402</v>
       </c>
       <c r="R63" t="n">
-        <v>7375874</v>
+        <v>7375948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670489</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135669405</v>
+        <v>135487698</v>
       </c>
       <c r="B64" t="n">
-        <v>58844</v>
+        <v>98297</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>208249</v>
+        <v>219815</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751402</v>
+        <v>751357</v>
       </c>
       <c r="R64" t="n">
-        <v>7375948</v>
+        <v>7376116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135487698</v>
+        <v>135493447</v>
       </c>
       <c r="B65" t="n">
-        <v>98297</v>
+        <v>108294</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219815</v>
+        <v>220083</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751357</v>
+        <v>751609</v>
       </c>
       <c r="R65" t="n">
-        <v>7376116</v>
+        <v>7376039</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135493447</v>
+        <v>135511789</v>
       </c>
       <c r="B66" t="n">
         <v>108294</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751609</v>
+        <v>751333</v>
       </c>
       <c r="R66" t="n">
-        <v>7376039</v>
+        <v>7375966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135511789</v>
+        <v>135487495</v>
       </c>
       <c r="B67" t="n">
-        <v>108294</v>
+        <v>111244</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751333</v>
+        <v>751361</v>
       </c>
       <c r="R67" t="n">
-        <v>7375966</v>
+        <v>7376128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135487495</v>
+        <v>135492620</v>
       </c>
       <c r="B68" t="n">
         <v>111244</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751361</v>
+        <v>751566</v>
       </c>
       <c r="R68" t="n">
-        <v>7376128</v>
+        <v>7376059</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135492620</v>
+        <v>135512174</v>
       </c>
       <c r="B69" t="n">
         <v>111244</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751566</v>
+        <v>751350</v>
       </c>
       <c r="R69" t="n">
-        <v>7376059</v>
+        <v>7375940</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135512174</v>
+        <v>135488283</v>
       </c>
       <c r="B70" t="n">
-        <v>111244</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751350</v>
+        <v>751338</v>
       </c>
       <c r="R70" t="n">
-        <v>7375940</v>
+        <v>7376087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,12 +7802,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7833,13 +7838,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135488283</v>
+        <v>135492603</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -7874,10 +7879,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751338</v>
+        <v>751552</v>
       </c>
       <c r="R71" t="n">
-        <v>7376087</v>
+        <v>7376059</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,11 +7917,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135492603</v>
+        <v>135510422</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>106398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751552</v>
+        <v>751264</v>
       </c>
       <c r="R72" t="n">
-        <v>7376059</v>
+        <v>7375973</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135510422</v>
+        <v>135487671</v>
       </c>
       <c r="B73" t="n">
-        <v>106398</v>
+        <v>98138</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751264</v>
+        <v>751354</v>
       </c>
       <c r="R73" t="n">
-        <v>7375973</v>
+        <v>7376126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135487671</v>
+        <v>135488071</v>
       </c>
       <c r="B74" t="n">
-        <v>98138</v>
+        <v>99298</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751354</v>
+        <v>751342</v>
       </c>
       <c r="R74" t="n">
-        <v>7376126</v>
+        <v>7376081</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135488071</v>
+        <v>135511436</v>
       </c>
       <c r="B75" t="n">
-        <v>99298</v>
+        <v>99082</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>223049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751342</v>
+        <v>751315</v>
       </c>
       <c r="R75" t="n">
-        <v>7376081</v>
+        <v>7375971</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,13 +8348,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135511436</v>
+        <v>135670818</v>
       </c>
       <c r="B76" t="n">
         <v>99082</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751315</v>
+        <v>751435</v>
       </c>
       <c r="R76" t="n">
-        <v>7375971</v>
+        <v>7375942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135670818</v>
+        <v>135491240</v>
       </c>
       <c r="B77" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751435</v>
+        <v>751305</v>
       </c>
       <c r="R77" t="n">
-        <v>7375942</v>
+        <v>7376101</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135491240</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135491240</v>
+        <v>135602173</v>
       </c>
       <c r="B78" t="n">
-        <v>98327</v>
+        <v>79464</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>223358</v>
+        <v>260591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751305</v>
+        <v>751327</v>
       </c>
       <c r="R78" t="n">
-        <v>7376101</v>
+        <v>7376136</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,12 +8623,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8653,113 +8658,6 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135602173</v>
-      </c>
-      <c r="B79" t="n">
-        <v>79464</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Lagnäsån, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>751327</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7376136</v>
-      </c>
-      <c r="S79" t="n">
-        <v>25</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8844,7 +8742,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135669405</v>
+        <v>135670489</v>
       </c>
       <c r="B63" t="n">
-        <v>58844</v>
+        <v>43388</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751402</v>
+        <v>751510</v>
       </c>
       <c r="R63" t="n">
-        <v>7375948</v>
+        <v>7375874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135670489</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135487698</v>
+        <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>98297</v>
+        <v>58844</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219815</v>
+        <v>208249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751357</v>
+        <v>751402</v>
       </c>
       <c r="R64" t="n">
-        <v>7376116</v>
+        <v>7375948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135493447</v>
+        <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>108294</v>
+        <v>98297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751609</v>
+        <v>751357</v>
       </c>
       <c r="R65" t="n">
-        <v>7376039</v>
+        <v>7376116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135511789</v>
+        <v>135493447</v>
       </c>
       <c r="B66" t="n">
         <v>108294</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751333</v>
+        <v>751609</v>
       </c>
       <c r="R66" t="n">
-        <v>7375966</v>
+        <v>7376039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135487495</v>
+        <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>111244</v>
+        <v>108294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751361</v>
+        <v>751333</v>
       </c>
       <c r="R67" t="n">
-        <v>7376128</v>
+        <v>7375966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135492620</v>
+        <v>135487495</v>
       </c>
       <c r="B68" t="n">
         <v>111244</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751566</v>
+        <v>751361</v>
       </c>
       <c r="R68" t="n">
-        <v>7376059</v>
+        <v>7376128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135512174</v>
+        <v>135492620</v>
       </c>
       <c r="B69" t="n">
         <v>111244</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751350</v>
+        <v>751566</v>
       </c>
       <c r="R69" t="n">
-        <v>7375940</v>
+        <v>7376059</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135488283</v>
+        <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>111244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751338</v>
+        <v>751350</v>
       </c>
       <c r="R70" t="n">
-        <v>7376087</v>
+        <v>7375940</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,17 +7802,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7838,13 +7833,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135492603</v>
+        <v>135488283</v>
       </c>
       <c r="B71" t="n">
         <v>99276</v>
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751552</v>
+        <v>751338</v>
       </c>
       <c r="R71" t="n">
-        <v>7376059</v>
+        <v>7376087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,6 +7912,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135510422</v>
+        <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>106398</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751264</v>
+        <v>751552</v>
       </c>
       <c r="R72" t="n">
-        <v>7375973</v>
+        <v>7376059</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135487671</v>
+        <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>98138</v>
+        <v>106398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751354</v>
+        <v>751264</v>
       </c>
       <c r="R73" t="n">
-        <v>7376126</v>
+        <v>7375973</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135488071</v>
+        <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>99298</v>
+        <v>98138</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751342</v>
+        <v>751354</v>
       </c>
       <c r="R74" t="n">
-        <v>7376081</v>
+        <v>7376126</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135511436</v>
+        <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99082</v>
+        <v>99298</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751315</v>
+        <v>751342</v>
       </c>
       <c r="R75" t="n">
-        <v>7375971</v>
+        <v>7376081</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,13 +8348,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135670818</v>
+        <v>135511436</v>
       </c>
       <c r="B76" t="n">
         <v>99082</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751435</v>
+        <v>751315</v>
       </c>
       <c r="R76" t="n">
-        <v>7375942</v>
+        <v>7375971</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135491240</v>
+        <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>98327</v>
+        <v>99082</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751305</v>
+        <v>751435</v>
       </c>
       <c r="R77" t="n">
-        <v>7376101</v>
+        <v>7375942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135602173</v>
+        <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>79464</v>
+        <v>98327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>260591</v>
+        <v>223358</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751327</v>
+        <v>751305</v>
       </c>
       <c r="R78" t="n">
-        <v>7376136</v>
+        <v>7376101</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,17 +8623,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8658,6 +8653,113 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8742,6 +8844,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>99274</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135511669</v>
       </c>
       <c r="B9" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>79980</v>
+        <v>79982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135494092</v>
       </c>
       <c r="B13" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>135494212</v>
       </c>
       <c r="B14" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135494377</v>
       </c>
       <c r="B15" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135494485</v>
       </c>
       <c r="B16" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135512295</v>
       </c>
       <c r="B17" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>135513277</v>
       </c>
       <c r="B18" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135513622</v>
       </c>
       <c r="B19" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101458</v>
+        <v>101475</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135602165</v>
       </c>
       <c r="B26" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135512444</v>
       </c>
       <c r="B27" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135493935</v>
       </c>
       <c r="B28" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135494039</v>
       </c>
       <c r="B29" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135602205</v>
       </c>
       <c r="B30" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135487454</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135487819</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>135488053</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>135488602</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135488683</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>135510447</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135567074</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135602198</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>135493576</v>
       </c>
       <c r="B39" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135493529</v>
       </c>
       <c r="B40" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>135513861</v>
       </c>
       <c r="B41" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>135511907</v>
       </c>
       <c r="B42" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>135490400</v>
       </c>
       <c r="B43" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>135487949</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135492288</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>135492904</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>135508817</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>135508144</v>
       </c>
       <c r="B48" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>135511007</v>
       </c>
       <c r="B49" t="n">
-        <v>12375</v>
+        <v>12377</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>135566886</v>
       </c>
       <c r="B50" t="n">
-        <v>12375</v>
+        <v>12377</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>135508608</v>
       </c>
       <c r="B51" t="n">
-        <v>12575</v>
+        <v>12577</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>135514248</v>
       </c>
       <c r="B52" t="n">
-        <v>12575</v>
+        <v>12577</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>135571094</v>
       </c>
       <c r="B53" t="n">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>135671375</v>
       </c>
       <c r="B54" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135672510</v>
       </c>
       <c r="B55" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>135488308</v>
       </c>
       <c r="B56" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>135493284</v>
       </c>
       <c r="B57" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135672524</v>
       </c>
       <c r="B58" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>135487574</v>
       </c>
       <c r="B59" t="n">
-        <v>58683</v>
+        <v>58685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>135491874</v>
       </c>
       <c r="B60" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>135508160</v>
       </c>
       <c r="B61" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>135487999</v>
       </c>
       <c r="B62" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135670489</v>
       </c>
       <c r="B63" t="n">
-        <v>43388</v>
+        <v>43390</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>135493447</v>
       </c>
       <c r="B66" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>135487495</v>
       </c>
       <c r="B68" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>135492620</v>
       </c>
       <c r="B69" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>135488283</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>135511436</v>
       </c>
       <c r="B76" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>135602173</v>
       </c>
       <c r="B79" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135511421</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135488970</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135490783</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135492457</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135511669</v>
       </c>
       <c r="B9" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>79982</v>
+        <v>79983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135494092</v>
       </c>
       <c r="B13" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>135494212</v>
       </c>
       <c r="B14" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135494377</v>
       </c>
       <c r="B15" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135494485</v>
       </c>
       <c r="B16" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135512295</v>
       </c>
       <c r="B17" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>135513277</v>
       </c>
       <c r="B18" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135513622</v>
       </c>
       <c r="B19" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101475</v>
+        <v>101477</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135602165</v>
       </c>
       <c r="B26" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135512444</v>
       </c>
       <c r="B27" t="n">
-        <v>96773</v>
+        <v>96774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>135493935</v>
       </c>
       <c r="B28" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>135494039</v>
       </c>
       <c r="B29" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135602205</v>
       </c>
       <c r="B30" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>135487454</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135487819</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>135488053</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>135488602</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>135488683</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>135510447</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135567074</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135602198</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>135493576</v>
       </c>
       <c r="B39" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135493529</v>
       </c>
       <c r="B40" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>135513861</v>
       </c>
       <c r="B41" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>135511907</v>
       </c>
       <c r="B42" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135670489</v>
+        <v>135669405</v>
       </c>
       <c r="B63" t="n">
-        <v>43390</v>
+        <v>58846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>201075</v>
+        <v>208249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751510</v>
+        <v>751402</v>
       </c>
       <c r="R63" t="n">
-        <v>7375874</v>
+        <v>7375948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670489</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135669405</v>
+        <v>135487698</v>
       </c>
       <c r="B64" t="n">
-        <v>58846</v>
+        <v>98315</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>208249</v>
+        <v>219815</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751402</v>
+        <v>751357</v>
       </c>
       <c r="R64" t="n">
-        <v>7375948</v>
+        <v>7376116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135487698</v>
+        <v>135493447</v>
       </c>
       <c r="B65" t="n">
-        <v>98314</v>
+        <v>108319</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219815</v>
+        <v>220083</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751357</v>
+        <v>751609</v>
       </c>
       <c r="R65" t="n">
-        <v>7376116</v>
+        <v>7376039</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,16 +7323,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135493447</v>
+        <v>135511789</v>
       </c>
       <c r="B66" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751609</v>
+        <v>751333</v>
       </c>
       <c r="R66" t="n">
-        <v>7376039</v>
+        <v>7375966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135511789</v>
+        <v>135487495</v>
       </c>
       <c r="B67" t="n">
-        <v>108317</v>
+        <v>111269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751333</v>
+        <v>751361</v>
       </c>
       <c r="R67" t="n">
-        <v>7375966</v>
+        <v>7376128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,16 +7527,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135487495</v>
+        <v>135492620</v>
       </c>
       <c r="B68" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751361</v>
+        <v>751566</v>
       </c>
       <c r="R68" t="n">
-        <v>7376128</v>
+        <v>7376059</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,16 +7629,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135492620</v>
+        <v>135512174</v>
       </c>
       <c r="B69" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751566</v>
+        <v>751350</v>
       </c>
       <c r="R69" t="n">
-        <v>7376059</v>
+        <v>7375940</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135512174</v>
+        <v>135488283</v>
       </c>
       <c r="B70" t="n">
-        <v>111267</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751350</v>
+        <v>751338</v>
       </c>
       <c r="R70" t="n">
-        <v>7375940</v>
+        <v>7376087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,12 +7802,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7833,16 +7838,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135488283</v>
+        <v>135492603</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7874,10 +7879,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751338</v>
+        <v>751552</v>
       </c>
       <c r="R71" t="n">
-        <v>7376087</v>
+        <v>7376059</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,11 +7917,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135492603</v>
+        <v>135510422</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>106420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751552</v>
+        <v>751264</v>
       </c>
       <c r="R72" t="n">
-        <v>7376059</v>
+        <v>7375973</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135510422</v>
+        <v>135487671</v>
       </c>
       <c r="B73" t="n">
-        <v>106418</v>
+        <v>98156</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751264</v>
+        <v>751354</v>
       </c>
       <c r="R73" t="n">
-        <v>7375973</v>
+        <v>7376126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135487671</v>
+        <v>135488071</v>
       </c>
       <c r="B74" t="n">
-        <v>98155</v>
+        <v>99316</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751354</v>
+        <v>751342</v>
       </c>
       <c r="R74" t="n">
-        <v>7376126</v>
+        <v>7376081</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135488071</v>
+        <v>135511436</v>
       </c>
       <c r="B75" t="n">
-        <v>99315</v>
+        <v>99100</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>223049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751342</v>
+        <v>751315</v>
       </c>
       <c r="R75" t="n">
-        <v>7376081</v>
+        <v>7375971</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,16 +8348,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135511436</v>
+        <v>135670818</v>
       </c>
       <c r="B76" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751315</v>
+        <v>751435</v>
       </c>
       <c r="R76" t="n">
-        <v>7375971</v>
+        <v>7375942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135670818</v>
+        <v>135491240</v>
       </c>
       <c r="B77" t="n">
-        <v>99099</v>
+        <v>98345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751435</v>
+        <v>751305</v>
       </c>
       <c r="R77" t="n">
-        <v>7375942</v>
+        <v>7376101</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135491240</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135491240</v>
+        <v>135602173</v>
       </c>
       <c r="B78" t="n">
-        <v>98344</v>
+        <v>79467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>223358</v>
+        <v>260591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751305</v>
+        <v>751327</v>
       </c>
       <c r="R78" t="n">
-        <v>7376101</v>
+        <v>7376136</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,12 +8623,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8653,113 +8658,6 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135602173</v>
-      </c>
-      <c r="B79" t="n">
-        <v>79466</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Lagnäsån, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>751327</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7376136</v>
-      </c>
-      <c r="S79" t="n">
-        <v>25</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8844,7 +8742,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135669405</v>
+        <v>135670489</v>
       </c>
       <c r="B63" t="n">
-        <v>58846</v>
+        <v>43390</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751402</v>
+        <v>751510</v>
       </c>
       <c r="R63" t="n">
-        <v>7375948</v>
+        <v>7375874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135670489</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135487698</v>
+        <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>98315</v>
+        <v>58846</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219815</v>
+        <v>208249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751357</v>
+        <v>751402</v>
       </c>
       <c r="R64" t="n">
-        <v>7376116</v>
+        <v>7375948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135493447</v>
+        <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>108319</v>
+        <v>98315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751609</v>
+        <v>751357</v>
       </c>
       <c r="R65" t="n">
-        <v>7376039</v>
+        <v>7376116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135511789</v>
+        <v>135493447</v>
       </c>
       <c r="B66" t="n">
         <v>108319</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751333</v>
+        <v>751609</v>
       </c>
       <c r="R66" t="n">
-        <v>7375966</v>
+        <v>7376039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135487495</v>
+        <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>111269</v>
+        <v>108319</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751361</v>
+        <v>751333</v>
       </c>
       <c r="R67" t="n">
-        <v>7376128</v>
+        <v>7375966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135492620</v>
+        <v>135487495</v>
       </c>
       <c r="B68" t="n">
         <v>111269</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751566</v>
+        <v>751361</v>
       </c>
       <c r="R68" t="n">
-        <v>7376059</v>
+        <v>7376128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135512174</v>
+        <v>135492620</v>
       </c>
       <c r="B69" t="n">
         <v>111269</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751350</v>
+        <v>751566</v>
       </c>
       <c r="R69" t="n">
-        <v>7375940</v>
+        <v>7376059</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135488283</v>
+        <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>111269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751338</v>
+        <v>751350</v>
       </c>
       <c r="R70" t="n">
-        <v>7376087</v>
+        <v>7375940</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,17 +7802,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7838,13 +7833,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135492603</v>
+        <v>135488283</v>
       </c>
       <c r="B71" t="n">
         <v>99294</v>
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751552</v>
+        <v>751338</v>
       </c>
       <c r="R71" t="n">
-        <v>7376059</v>
+        <v>7376087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,6 +7912,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135510422</v>
+        <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>106420</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751264</v>
+        <v>751552</v>
       </c>
       <c r="R72" t="n">
-        <v>7375973</v>
+        <v>7376059</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135487671</v>
+        <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>98156</v>
+        <v>106420</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751354</v>
+        <v>751264</v>
       </c>
       <c r="R73" t="n">
-        <v>7376126</v>
+        <v>7375973</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135488071</v>
+        <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>99316</v>
+        <v>98156</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751342</v>
+        <v>751354</v>
       </c>
       <c r="R74" t="n">
-        <v>7376081</v>
+        <v>7376126</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135511436</v>
+        <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99100</v>
+        <v>99316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751315</v>
+        <v>751342</v>
       </c>
       <c r="R75" t="n">
-        <v>7375971</v>
+        <v>7376081</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,13 +8348,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135670818</v>
+        <v>135511436</v>
       </c>
       <c r="B76" t="n">
         <v>99100</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751435</v>
+        <v>751315</v>
       </c>
       <c r="R76" t="n">
-        <v>7375942</v>
+        <v>7375971</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135491240</v>
+        <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>98345</v>
+        <v>99100</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751305</v>
+        <v>751435</v>
       </c>
       <c r="R77" t="n">
-        <v>7376101</v>
+        <v>7375942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135602173</v>
+        <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>79467</v>
+        <v>98345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>260591</v>
+        <v>223358</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751327</v>
+        <v>751305</v>
       </c>
       <c r="R78" t="n">
-        <v>7376136</v>
+        <v>7376101</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,17 +8623,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8658,6 +8653,113 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8742,6 +8844,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101477</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>135602165</v>
       </c>
       <c r="B26" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>135602205</v>
       </c>
       <c r="B30" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135670489</v>
+        <v>135669405</v>
       </c>
       <c r="B63" t="n">
-        <v>43390</v>
+        <v>58846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>201075</v>
+        <v>208249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751510</v>
+        <v>751402</v>
       </c>
       <c r="R63" t="n">
-        <v>7375874</v>
+        <v>7375948</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670489</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135669405</v>
+        <v>135487698</v>
       </c>
       <c r="B64" t="n">
-        <v>58846</v>
+        <v>98315</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>208249</v>
+        <v>219815</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751402</v>
+        <v>751357</v>
       </c>
       <c r="R64" t="n">
-        <v>7375948</v>
+        <v>7376116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135487698</v>
+        <v>135493447</v>
       </c>
       <c r="B65" t="n">
-        <v>98315</v>
+        <v>108319</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219815</v>
+        <v>220083</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751357</v>
+        <v>751609</v>
       </c>
       <c r="R65" t="n">
-        <v>7376116</v>
+        <v>7376039</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135493447</v>
+        <v>135511789</v>
       </c>
       <c r="B66" t="n">
         <v>108319</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751609</v>
+        <v>751333</v>
       </c>
       <c r="R66" t="n">
-        <v>7376039</v>
+        <v>7375966</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135511789</v>
+        <v>135487495</v>
       </c>
       <c r="B67" t="n">
-        <v>108319</v>
+        <v>111269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220083</v>
+        <v>220240</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751333</v>
+        <v>751361</v>
       </c>
       <c r="R67" t="n">
-        <v>7375966</v>
+        <v>7376128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135487495</v>
+        <v>135492620</v>
       </c>
       <c r="B68" t="n">
         <v>111269</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751361</v>
+        <v>751566</v>
       </c>
       <c r="R68" t="n">
-        <v>7376128</v>
+        <v>7376059</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135492620</v>
+        <v>135512174</v>
       </c>
       <c r="B69" t="n">
         <v>111269</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751566</v>
+        <v>751350</v>
       </c>
       <c r="R69" t="n">
-        <v>7376059</v>
+        <v>7375940</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135512174</v>
+        <v>135488283</v>
       </c>
       <c r="B70" t="n">
-        <v>111269</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220240</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751350</v>
+        <v>751338</v>
       </c>
       <c r="R70" t="n">
-        <v>7375940</v>
+        <v>7376087</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,12 +7802,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7833,13 +7838,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135488283</v>
+        <v>135492603</v>
       </c>
       <c r="B71" t="n">
         <v>99294</v>
@@ -7874,10 +7879,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751338</v>
+        <v>751552</v>
       </c>
       <c r="R71" t="n">
-        <v>7376087</v>
+        <v>7376059</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7912,11 +7917,6 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135492603</v>
+        <v>135510422</v>
       </c>
       <c r="B72" t="n">
-        <v>99294</v>
+        <v>106420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751552</v>
+        <v>751264</v>
       </c>
       <c r="R72" t="n">
-        <v>7376059</v>
+        <v>7375973</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135510422</v>
+        <v>135487671</v>
       </c>
       <c r="B73" t="n">
-        <v>106420</v>
+        <v>98156</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751264</v>
+        <v>751354</v>
       </c>
       <c r="R73" t="n">
-        <v>7375973</v>
+        <v>7376126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135487671</v>
+        <v>135488071</v>
       </c>
       <c r="B74" t="n">
-        <v>98156</v>
+        <v>99316</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751354</v>
+        <v>751342</v>
       </c>
       <c r="R74" t="n">
-        <v>7376126</v>
+        <v>7376081</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135488071</v>
+        <v>135511436</v>
       </c>
       <c r="B75" t="n">
-        <v>99316</v>
+        <v>99100</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>223049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751342</v>
+        <v>751315</v>
       </c>
       <c r="R75" t="n">
-        <v>7376081</v>
+        <v>7375971</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,16 +8348,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135511436</v>
+        <v>135670818</v>
       </c>
       <c r="B76" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751315</v>
+        <v>751435</v>
       </c>
       <c r="R76" t="n">
-        <v>7375971</v>
+        <v>7375942</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135670818</v>
+        <v>135491240</v>
       </c>
       <c r="B77" t="n">
-        <v>99101</v>
+        <v>98345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751435</v>
+        <v>751305</v>
       </c>
       <c r="R77" t="n">
-        <v>7375942</v>
+        <v>7376101</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135491240</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135491240</v>
+        <v>135602173</v>
       </c>
       <c r="B78" t="n">
-        <v>98345</v>
+        <v>79467</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>223358</v>
+        <v>260591</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751305</v>
+        <v>751327</v>
       </c>
       <c r="R78" t="n">
-        <v>7376101</v>
+        <v>7376136</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,12 +8623,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8653,113 +8658,6 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135602173</v>
-      </c>
-      <c r="B79" t="n">
-        <v>79467</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Lagnäsån, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>751327</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7376136</v>
-      </c>
-      <c r="S79" t="n">
-        <v>25</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8844,7 +8742,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79983</v>
+        <v>79984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79983</v>
+        <v>79984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>79983</v>
+        <v>79984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>101479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>135671375</v>
       </c>
       <c r="B54" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135672510</v>
       </c>
       <c r="B55" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135672524</v>
       </c>
       <c r="B58" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7023,32 +7023,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135669405</v>
+        <v>135670489</v>
       </c>
       <c r="B63" t="n">
-        <v>58846</v>
+        <v>43391</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>201075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7058,10 +7058,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>751402</v>
+        <v>751510</v>
       </c>
       <c r="R63" t="n">
-        <v>7375948</v>
+        <v>7375874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7119,16 +7119,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135669405</t>
+          <t>https://artportalen.se/Sighting/135670489</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135487698</v>
+        <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>98315</v>
+        <v>58847</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219815</v>
+        <v>208249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>751357</v>
+        <v>751402</v>
       </c>
       <c r="R64" t="n">
-        <v>7376116</v>
+        <v>7375948</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7221,16 +7221,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487698</t>
+          <t>https://artportalen.se/Sighting/135669405</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135493447</v>
+        <v>135487698</v>
       </c>
       <c r="B65" t="n">
-        <v>108319</v>
+        <v>98315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7238,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>751609</v>
+        <v>751357</v>
       </c>
       <c r="R65" t="n">
-        <v>7376039</v>
+        <v>7376116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7323,13 +7323,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135493447</t>
+          <t>https://artportalen.se/Sighting/135487698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135511789</v>
+        <v>135493447</v>
       </c>
       <c r="B66" t="n">
         <v>108319</v>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>751333</v>
+        <v>751609</v>
       </c>
       <c r="R66" t="n">
-        <v>7375966</v>
+        <v>7376039</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7425,16 +7425,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511789</t>
+          <t>https://artportalen.se/Sighting/135493447</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135487495</v>
+        <v>135511789</v>
       </c>
       <c r="B67" t="n">
-        <v>111269</v>
+        <v>108319</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7442,21 +7442,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>751361</v>
+        <v>751333</v>
       </c>
       <c r="R67" t="n">
-        <v>7376128</v>
+        <v>7375966</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,13 +7527,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487495</t>
+          <t>https://artportalen.se/Sighting/135511789</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135492620</v>
+        <v>135487495</v>
       </c>
       <c r="B68" t="n">
         <v>111269</v>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>751566</v>
+        <v>751361</v>
       </c>
       <c r="R68" t="n">
-        <v>7376059</v>
+        <v>7376128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7629,13 +7629,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492620</t>
+          <t>https://artportalen.se/Sighting/135487495</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135512174</v>
+        <v>135492620</v>
       </c>
       <c r="B69" t="n">
         <v>111269</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>751350</v>
+        <v>751566</v>
       </c>
       <c r="R69" t="n">
-        <v>7375940</v>
+        <v>7376059</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7731,38 +7731,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135512174</t>
+          <t>https://artportalen.se/Sighting/135492620</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135488283</v>
+        <v>135512174</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>111269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>751338</v>
+        <v>751350</v>
       </c>
       <c r="R70" t="n">
-        <v>7376087</v>
+        <v>7375940</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,17 +7802,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växtplats 1</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7838,13 +7833,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488283</t>
+          <t>https://artportalen.se/Sighting/135512174</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135492603</v>
+        <v>135488283</v>
       </c>
       <c r="B71" t="n">
         <v>99294</v>
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>751552</v>
+        <v>751338</v>
       </c>
       <c r="R71" t="n">
-        <v>7376059</v>
+        <v>7376087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7917,6 +7912,11 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växtplats 1</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7940,38 +7940,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135492603</t>
+          <t>https://artportalen.se/Sighting/135488283</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135510422</v>
+        <v>135492603</v>
       </c>
       <c r="B72" t="n">
-        <v>106420</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>751264</v>
+        <v>751552</v>
       </c>
       <c r="R72" t="n">
-        <v>7375973</v>
+        <v>7376059</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8042,16 +8042,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135510422</t>
+          <t>https://artportalen.se/Sighting/135492603</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135487671</v>
+        <v>135510422</v>
       </c>
       <c r="B73" t="n">
-        <v>98156</v>
+        <v>106420</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8059,21 +8059,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8083,10 +8083,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>751354</v>
+        <v>751264</v>
       </c>
       <c r="R73" t="n">
-        <v>7376126</v>
+        <v>7375973</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8144,16 +8144,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135487671</t>
+          <t>https://artportalen.se/Sighting/135510422</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135488071</v>
+        <v>135487671</v>
       </c>
       <c r="B74" t="n">
-        <v>99316</v>
+        <v>98156</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8161,21 +8161,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>751342</v>
+        <v>751354</v>
       </c>
       <c r="R74" t="n">
-        <v>7376081</v>
+        <v>7376126</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8246,16 +8246,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135488071</t>
+          <t>https://artportalen.se/Sighting/135487671</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135511436</v>
+        <v>135488071</v>
       </c>
       <c r="B75" t="n">
-        <v>99100</v>
+        <v>99316</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>751315</v>
+        <v>751342</v>
       </c>
       <c r="R75" t="n">
-        <v>7375971</v>
+        <v>7376081</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,16 +8348,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135511436</t>
+          <t>https://artportalen.se/Sighting/135488071</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135670818</v>
+        <v>135511436</v>
       </c>
       <c r="B76" t="n">
-        <v>99101</v>
+        <v>99100</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>751435</v>
+        <v>751315</v>
       </c>
       <c r="R76" t="n">
-        <v>7375942</v>
+        <v>7375971</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8450,16 +8450,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135670818</t>
+          <t>https://artportalen.se/Sighting/135511436</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135491240</v>
+        <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>98345</v>
+        <v>99102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8467,21 +8467,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>223358</v>
+        <v>223049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>751305</v>
+        <v>751435</v>
       </c>
       <c r="R77" t="n">
-        <v>7376101</v>
+        <v>7375942</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8552,54 +8552,54 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135491240</t>
+          <t>https://artportalen.se/Sighting/135670818</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135602173</v>
+        <v>135491240</v>
       </c>
       <c r="B78" t="n">
-        <v>79467</v>
+        <v>98345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>260591</v>
+        <v>223358</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagnäsån, Lu lm</t>
+          <t>Lagnäsån, Lagnäsån, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>751327</v>
+        <v>751305</v>
       </c>
       <c r="R78" t="n">
-        <v>7376136</v>
+        <v>7376101</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8623,17 +8623,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8658,6 +8653,113 @@
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491240</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135602173</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lagnäsån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>751327</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7376136</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135602173</t>
         </is>
@@ -8742,6 +8844,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101479</v>
+        <v>101485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>135671375</v>
       </c>
       <c r="B54" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135672510</v>
       </c>
       <c r="B55" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135672524</v>
       </c>
       <c r="B58" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>58847</v>
+        <v>58851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 31827-2026 artfynd.xlsx
+++ b/artfynd/A 31827-2026 artfynd.xlsx
@@ -1499,7 +1499,7 @@
         <v>135668795</v>
       </c>
       <c r="B10" t="n">
-        <v>79988</v>
+        <v>79989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135671559</v>
       </c>
       <c r="B11" t="n">
-        <v>79988</v>
+        <v>79989</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135675709</v>
       </c>
       <c r="B12" t="n">
-        <v>79988</v>
+        <v>79989</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>135670886</v>
       </c>
       <c r="B20" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>135671019</v>
       </c>
       <c r="B21" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135675710</v>
       </c>
       <c r="B22" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>135675711</v>
       </c>
       <c r="B23" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>135675712</v>
       </c>
       <c r="B24" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>135675713</v>
       </c>
       <c r="B25" t="n">
-        <v>101485</v>
+        <v>101486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>135671375</v>
       </c>
       <c r="B54" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>135672510</v>
       </c>
       <c r="B55" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>135672524</v>
       </c>
       <c r="B58" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135669405</v>
       </c>
       <c r="B64" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>135670818</v>
       </c>
       <c r="B77" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
